--- a/research/traditional_assets/database/data/uganda/uganda_power.xlsx
+++ b/research/traditional_assets/database/data/uganda/uganda_power.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1037517413541845</v>
+        <v>0.1034719861301219</v>
       </c>
       <c r="C2">
-        <v>202.8656468719928</v>
+        <v>200.9639544592594</v>
       </c>
       <c r="D2">
-        <v>192.6656468719928</v>
+        <v>192.7849544592594</v>
       </c>
       <c r="E2">
-        <v>-20.1</v>
+        <v>-18.079</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.021</v>
       </c>
       <c r="G2">
         <v>10.2</v>
@@ -1451,28 +1451,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1016563</v>
       </c>
       <c r="N2">
-        <v>47.59999999999997</v>
+        <v>47.49834369999996</v>
       </c>
       <c r="O2">
-        <v>14.27999999999999</v>
+        <v>14.24950310999999</v>
       </c>
       <c r="P2">
-        <v>33.31999999999998</v>
+        <v>33.24884058999997</v>
       </c>
       <c r="Q2">
-        <v>157.72</v>
+        <v>157.64884059</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1037517413541845</v>
+        <v>0.1041615011415373</v>
       </c>
       <c r="T2">
-        <v>0.4454993697880389</v>
+        <v>0.4486493653319947</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>468.2444668948208</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1034719861301219</v>
+        <v>0.1031922309060594</v>
       </c>
       <c r="C3">
-        <v>200.9639544592594</v>
+        <v>199.0624098997693</v>
       </c>
       <c r="D3">
-        <v>192.7849544592594</v>
+        <v>192.9044098997693</v>
       </c>
       <c r="E3">
-        <v>-18.079</v>
+        <v>-16.058</v>
       </c>
       <c r="F3">
-        <v>2.021</v>
+        <v>4.042</v>
       </c>
       <c r="G3">
         <v>10.2</v>
@@ -1533,28 +1533,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M3">
-        <v>0.1016563</v>
+        <v>0.2033126</v>
       </c>
       <c r="N3">
-        <v>47.49834369999996</v>
+        <v>47.39668739999997</v>
       </c>
       <c r="O3">
-        <v>14.24950310999999</v>
+        <v>14.21900621999999</v>
       </c>
       <c r="P3">
-        <v>33.24884058999997</v>
+        <v>33.17768117999998</v>
       </c>
       <c r="Q3">
-        <v>157.64884059</v>
+        <v>157.57768118</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1041615011415373</v>
+        <v>0.10457962337353</v>
       </c>
       <c r="T3">
-        <v>0.4486493653319947</v>
+        <v>0.4518636464992966</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>468.2444668948208</v>
+        <v>234.1222334474104</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1031922309060594</v>
+        <v>0.1029124756819969</v>
       </c>
       <c r="C4">
-        <v>199.0624098997693</v>
+        <v>197.1610134685361</v>
       </c>
       <c r="D4">
-        <v>192.9044098997693</v>
+        <v>193.0240134685361</v>
       </c>
       <c r="E4">
-        <v>-16.058</v>
+        <v>-14.037</v>
       </c>
       <c r="F4">
-        <v>4.042</v>
+        <v>6.063</v>
       </c>
       <c r="G4">
         <v>10.2</v>
@@ -1615,28 +1615,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M4">
-        <v>0.2033126</v>
+        <v>0.3049689</v>
       </c>
       <c r="N4">
-        <v>47.39668739999997</v>
+        <v>47.29503109999997</v>
       </c>
       <c r="O4">
-        <v>14.21900621999999</v>
+        <v>14.18850932999999</v>
       </c>
       <c r="P4">
-        <v>33.17768117999998</v>
+        <v>33.10652176999998</v>
       </c>
       <c r="Q4">
-        <v>157.57768118</v>
+        <v>157.50652177</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.10457962337353</v>
+        <v>0.105006366682471</v>
       </c>
       <c r="T4">
-        <v>0.4518636464992966</v>
+        <v>0.4551442015050995</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>234.1222334474104</v>
+        <v>156.0814889649403</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1029124756819969</v>
+        <v>0.1026327204579343</v>
       </c>
       <c r="C5">
-        <v>197.1610134685361</v>
+        <v>195.2597654412558</v>
       </c>
       <c r="D5">
-        <v>193.0240134685361</v>
+        <v>193.1437654412558</v>
       </c>
       <c r="E5">
-        <v>-14.037</v>
+        <v>-12.016</v>
       </c>
       <c r="F5">
-        <v>6.063</v>
+        <v>8.084</v>
       </c>
       <c r="G5">
         <v>10.2</v>
@@ -1697,28 +1697,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M5">
-        <v>0.3049689</v>
+        <v>0.4066252</v>
       </c>
       <c r="N5">
-        <v>47.29503109999997</v>
+        <v>47.19337479999997</v>
       </c>
       <c r="O5">
-        <v>14.18850932999999</v>
+        <v>14.15801243999999</v>
       </c>
       <c r="P5">
-        <v>33.10652176999998</v>
+        <v>33.03536235999998</v>
       </c>
       <c r="Q5">
-        <v>157.50652177</v>
+        <v>157.43536236</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.105006366682471</v>
+        <v>0.1054420004770149</v>
       </c>
       <c r="T5">
-        <v>0.4551442015050995</v>
+        <v>0.4584931014068566</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>156.0814889649403</v>
+        <v>117.0611167237052</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1026327204579343</v>
+        <v>0.1023529652338717</v>
       </c>
       <c r="C6">
-        <v>195.2597654412558</v>
+        <v>193.3586660943091</v>
       </c>
       <c r="D6">
-        <v>193.1437654412558</v>
+        <v>193.2636660943091</v>
       </c>
       <c r="E6">
-        <v>-12.016</v>
+        <v>-9.995000000000001</v>
       </c>
       <c r="F6">
-        <v>8.084</v>
+        <v>10.105</v>
       </c>
       <c r="G6">
         <v>10.2</v>
@@ -1779,28 +1779,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M6">
-        <v>0.4066252</v>
+        <v>0.5082814999999999</v>
       </c>
       <c r="N6">
-        <v>47.19337479999997</v>
+        <v>47.09171849999996</v>
       </c>
       <c r="O6">
-        <v>14.15801243999999</v>
+        <v>14.12751554999999</v>
       </c>
       <c r="P6">
-        <v>33.03536235999998</v>
+        <v>32.96420294999997</v>
       </c>
       <c r="Q6">
-        <v>157.43536236</v>
+        <v>157.36420295</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1054420004770149</v>
+        <v>0.1058868055093387</v>
       </c>
       <c r="T6">
-        <v>0.4584931014068566</v>
+        <v>0.4619125044644403</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>117.0611167237052</v>
+        <v>93.64889337896416</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1023529652338717</v>
+        <v>0.1020732100098092</v>
       </c>
       <c r="C7">
-        <v>193.3586660943091</v>
+        <v>191.4577157047632</v>
       </c>
       <c r="D7">
-        <v>193.2636660943091</v>
+        <v>193.3837157047632</v>
       </c>
       <c r="E7">
-        <v>-9.995000000000001</v>
+        <v>-7.974</v>
       </c>
       <c r="F7">
-        <v>10.105</v>
+        <v>12.126</v>
       </c>
       <c r="G7">
         <v>10.2</v>
@@ -1861,28 +1861,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M7">
-        <v>0.5082814999999999</v>
+        <v>0.6099378000000001</v>
       </c>
       <c r="N7">
-        <v>47.09171849999996</v>
+        <v>46.99006219999997</v>
       </c>
       <c r="O7">
-        <v>14.12751554999999</v>
+        <v>14.09701865999999</v>
       </c>
       <c r="P7">
-        <v>32.96420294999997</v>
+        <v>32.89304353999998</v>
       </c>
       <c r="Q7">
-        <v>157.36420295</v>
+        <v>157.29304354</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1058868055093387</v>
+        <v>0.1063410744785204</v>
       </c>
       <c r="T7">
-        <v>0.4619125044644403</v>
+        <v>0.4654046607785682</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>93.64889337896416</v>
+        <v>78.04074448247012</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1020732100098092</v>
+        <v>0.1017934547857467</v>
       </c>
       <c r="C8">
-        <v>191.4577157047632</v>
+        <v>189.5569145503744</v>
       </c>
       <c r="D8">
-        <v>193.3837157047632</v>
+        <v>193.5039145503744</v>
       </c>
       <c r="E8">
-        <v>-7.974000000000002</v>
+        <v>-5.953000000000003</v>
       </c>
       <c r="F8">
-        <v>12.126</v>
+        <v>14.147</v>
       </c>
       <c r="G8">
         <v>10.2</v>
@@ -1943,28 +1943,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M8">
-        <v>0.6099378</v>
+        <v>0.7115940999999999</v>
       </c>
       <c r="N8">
-        <v>46.99006219999997</v>
+        <v>46.88840589999997</v>
       </c>
       <c r="O8">
-        <v>14.09701865999999</v>
+        <v>14.06652176999999</v>
       </c>
       <c r="P8">
-        <v>32.89304353999998</v>
+        <v>32.82188412999998</v>
       </c>
       <c r="Q8">
-        <v>157.29304354</v>
+        <v>157.22188413</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1063410744785204</v>
+        <v>0.1068051126728459</v>
       </c>
       <c r="T8">
-        <v>0.4654046607785682</v>
+        <v>0.468971917228484</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>78.04074448247013</v>
+        <v>66.89206669926011</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1017934547857466</v>
+        <v>0.1015136995616841</v>
       </c>
       <c r="C9">
-        <v>189.5569145503744</v>
+        <v>187.6562629095899</v>
       </c>
       <c r="D9">
-        <v>193.5039145503744</v>
+        <v>193.6242629095899</v>
       </c>
       <c r="E9">
-        <v>-5.953000000000001</v>
+        <v>-3.932000000000002</v>
       </c>
       <c r="F9">
-        <v>14.147</v>
+        <v>16.168</v>
       </c>
       <c r="G9">
         <v>10.2</v>
@@ -2025,28 +2025,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M9">
-        <v>0.7115941</v>
+        <v>0.8132503999999999</v>
       </c>
       <c r="N9">
-        <v>46.88840589999997</v>
+        <v>46.78674959999996</v>
       </c>
       <c r="O9">
-        <v>14.06652176999999</v>
+        <v>14.03602487999999</v>
       </c>
       <c r="P9">
-        <v>32.82188412999998</v>
+        <v>32.75072471999998</v>
       </c>
       <c r="Q9">
-        <v>157.22188413</v>
+        <v>157.15072472</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1068051126728459</v>
+        <v>0.1072792386540044</v>
       </c>
       <c r="T9">
-        <v>0.468971917228484</v>
+        <v>0.4726167227316587</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>66.89206669926011</v>
+        <v>58.5305583618526</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1015136995616841</v>
+        <v>0.1012339443376215</v>
       </c>
       <c r="C10">
-        <v>187.6562629095899</v>
+        <v>185.7557610615499</v>
       </c>
       <c r="D10">
-        <v>193.6242629095899</v>
+        <v>193.7447610615499</v>
       </c>
       <c r="E10">
-        <v>-3.932000000000002</v>
+        <v>-1.911000000000001</v>
       </c>
       <c r="F10">
-        <v>16.168</v>
+        <v>18.189</v>
       </c>
       <c r="G10">
         <v>10.2</v>
@@ -2107,28 +2107,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M10">
-        <v>0.8132503999999999</v>
+        <v>0.9149067</v>
       </c>
       <c r="N10">
-        <v>46.78674959999996</v>
+        <v>46.68509329999996</v>
       </c>
       <c r="O10">
-        <v>14.03602487999999</v>
+        <v>14.00552798999999</v>
       </c>
       <c r="P10">
-        <v>32.75072471999998</v>
+        <v>32.67956530999997</v>
       </c>
       <c r="Q10">
-        <v>157.15072472</v>
+        <v>157.07956531</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1072792386540044</v>
+        <v>0.1077637849863973</v>
       </c>
       <c r="T10">
-        <v>0.4726167227316587</v>
+        <v>0.4763416338502877</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>58.5305583618526</v>
+        <v>52.02716298831341</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1012339443376215</v>
+        <v>0.100954189113559</v>
       </c>
       <c r="C11">
-        <v>185.7557610615499</v>
+        <v>183.85540928609</v>
       </c>
       <c r="D11">
-        <v>193.7447610615499</v>
+        <v>193.8654092860901</v>
       </c>
       <c r="E11">
-        <v>-1.911000000000001</v>
+        <v>0.1099999999999959</v>
       </c>
       <c r="F11">
-        <v>18.189</v>
+        <v>20.21</v>
       </c>
       <c r="G11">
         <v>10.2</v>
@@ -2189,28 +2189,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M11">
-        <v>0.9149067</v>
+        <v>1.016563</v>
       </c>
       <c r="N11">
-        <v>46.68509329999996</v>
+        <v>46.58343699999997</v>
       </c>
       <c r="O11">
-        <v>14.00552798999999</v>
+        <v>13.97503109999999</v>
       </c>
       <c r="P11">
-        <v>32.67956530999997</v>
+        <v>32.60840589999998</v>
       </c>
       <c r="Q11">
-        <v>157.07956531</v>
+        <v>157.0084059</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1077637849863973</v>
+        <v>0.1082590990150655</v>
       </c>
       <c r="T11">
-        <v>0.4763416338502877</v>
+        <v>0.480149320771553</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>52.02716298831341</v>
+        <v>46.82444668948208</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.100954189113559</v>
+        <v>0.1006744338894964</v>
       </c>
       <c r="C12">
-        <v>183.85540928609</v>
+        <v>181.9552078637435</v>
       </c>
       <c r="D12">
-        <v>193.8654092860901</v>
+        <v>193.9862078637435</v>
       </c>
       <c r="E12">
-        <v>0.1099999999999994</v>
+        <v>2.130999999999997</v>
       </c>
       <c r="F12">
-        <v>20.21</v>
+        <v>22.231</v>
       </c>
       <c r="G12">
         <v>10.2</v>
@@ -2271,28 +2271,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M12">
-        <v>1.016563</v>
+        <v>1.1182193</v>
       </c>
       <c r="N12">
-        <v>46.58343699999997</v>
+        <v>46.48178069999997</v>
       </c>
       <c r="O12">
-        <v>13.97503109999999</v>
+        <v>13.94453420999999</v>
       </c>
       <c r="P12">
-        <v>32.60840589999998</v>
+        <v>32.53724648999997</v>
       </c>
       <c r="Q12">
-        <v>157.0084059</v>
+        <v>156.93724649</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1082590990150655</v>
+        <v>0.1087655436960634</v>
       </c>
       <c r="T12">
-        <v>0.480149320771553</v>
+        <v>0.484042573691049</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>46.82444668948208</v>
+        <v>42.56767880862007</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1006744338894964</v>
+        <v>0.1003946786654339</v>
       </c>
       <c r="C13">
-        <v>181.9552078637435</v>
+        <v>180.0551570757429</v>
       </c>
       <c r="D13">
-        <v>193.9862078637435</v>
+        <v>194.1071570757429</v>
       </c>
       <c r="E13">
-        <v>2.130999999999997</v>
+        <v>4.151999999999997</v>
       </c>
       <c r="F13">
-        <v>22.231</v>
+        <v>24.252</v>
       </c>
       <c r="G13">
         <v>10.2</v>
@@ -2353,28 +2353,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M13">
-        <v>1.1182193</v>
+        <v>1.2198756</v>
       </c>
       <c r="N13">
-        <v>46.48178069999997</v>
+        <v>46.38012439999996</v>
       </c>
       <c r="O13">
-        <v>13.94453420999999</v>
+        <v>13.91403731999999</v>
       </c>
       <c r="P13">
-        <v>32.53724648999997</v>
+        <v>32.46608707999997</v>
       </c>
       <c r="Q13">
-        <v>156.93724649</v>
+        <v>156.86608708</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1087655436960634</v>
+        <v>0.1092834984834476</v>
       </c>
       <c r="T13">
-        <v>0.484042573691049</v>
+        <v>0.4880243096314426</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>42.56767880862007</v>
+        <v>39.02037224123506</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1003946786654339</v>
+        <v>0.1001149234413713</v>
       </c>
       <c r="C14">
-        <v>180.0551570757429</v>
+        <v>178.1552572040229</v>
       </c>
       <c r="D14">
-        <v>194.1071570757429</v>
+        <v>194.2282572040229</v>
       </c>
       <c r="E14">
-        <v>4.151999999999997</v>
+        <v>6.172999999999998</v>
       </c>
       <c r="F14">
-        <v>24.252</v>
+        <v>26.273</v>
       </c>
       <c r="G14">
         <v>10.2</v>
@@ -2435,28 +2435,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M14">
-        <v>1.2198756</v>
+        <v>1.3215319</v>
       </c>
       <c r="N14">
-        <v>46.38012439999996</v>
+        <v>46.27846809999997</v>
       </c>
       <c r="O14">
-        <v>13.91403731999999</v>
+        <v>13.88354042999999</v>
       </c>
       <c r="P14">
-        <v>32.46608707999997</v>
+        <v>32.39492766999998</v>
       </c>
       <c r="Q14">
-        <v>156.86608708</v>
+        <v>156.79492767</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1092834984834476</v>
+        <v>0.1098133602774383</v>
       </c>
       <c r="T14">
-        <v>0.4880243096314426</v>
+        <v>0.4920975797313855</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>39.02037224123506</v>
+        <v>36.01880514575545</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1001149234413713</v>
+        <v>0.09983516821730877</v>
       </c>
       <c r="C15">
-        <v>178.1552572040229</v>
+        <v>176.2555085312221</v>
       </c>
       <c r="D15">
-        <v>194.2282572040229</v>
+        <v>194.3495085312221</v>
       </c>
       <c r="E15">
-        <v>6.172999999999998</v>
+        <v>8.193999999999999</v>
       </c>
       <c r="F15">
-        <v>26.273</v>
+        <v>28.294</v>
       </c>
       <c r="G15">
         <v>10.2</v>
@@ -2517,28 +2517,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M15">
-        <v>1.3215319</v>
+        <v>1.4231882</v>
       </c>
       <c r="N15">
-        <v>46.27846809999997</v>
+        <v>46.17681179999997</v>
       </c>
       <c r="O15">
-        <v>13.88354042999999</v>
+        <v>13.85304353999999</v>
       </c>
       <c r="P15">
-        <v>32.39492766999998</v>
+        <v>32.32376825999998</v>
       </c>
       <c r="Q15">
-        <v>156.79492767</v>
+        <v>156.72376826</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1098133602774383</v>
+        <v>0.1103555444387311</v>
       </c>
       <c r="T15">
-        <v>0.4920975797313855</v>
+        <v>0.4962655770429549</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>36.01880514575545</v>
+        <v>33.44603334963006</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09983516821730877</v>
+        <v>0.0995554129932462</v>
       </c>
       <c r="C16">
-        <v>176.2555085312221</v>
+        <v>174.3559113406852</v>
       </c>
       <c r="D16">
-        <v>194.3495085312221</v>
+        <v>194.4709113406852</v>
       </c>
       <c r="E16">
-        <v>8.193999999999999</v>
+        <v>10.215</v>
       </c>
       <c r="F16">
-        <v>28.294</v>
+        <v>30.315</v>
       </c>
       <c r="G16">
         <v>10.2</v>
@@ -2599,28 +2599,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M16">
-        <v>1.4231882</v>
+        <v>1.5248445</v>
       </c>
       <c r="N16">
-        <v>46.17681179999997</v>
+        <v>46.07515549999997</v>
       </c>
       <c r="O16">
-        <v>13.85304353999999</v>
+        <v>13.82254664999999</v>
       </c>
       <c r="P16">
-        <v>32.32376825999998</v>
+        <v>32.25260884999997</v>
       </c>
       <c r="Q16">
-        <v>156.72376826</v>
+        <v>156.65260885</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1103555444387311</v>
+        <v>0.1109104858744073</v>
       </c>
       <c r="T16">
-        <v>0.4962655770429549</v>
+        <v>0.5005316448795025</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>33.44603334963006</v>
+        <v>31.21629779298805</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0995554129932462</v>
+        <v>0.09927565776918366</v>
       </c>
       <c r="C17">
-        <v>174.3559113406852</v>
+        <v>172.4564659164654</v>
       </c>
       <c r="D17">
-        <v>194.4709113406852</v>
+        <v>194.5924659164654</v>
       </c>
       <c r="E17">
-        <v>10.215</v>
+        <v>12.236</v>
       </c>
       <c r="F17">
-        <v>30.315</v>
+        <v>32.336</v>
       </c>
       <c r="G17">
         <v>10.2</v>
@@ -2681,28 +2681,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M17">
-        <v>1.5248445</v>
+        <v>1.6265008</v>
       </c>
       <c r="N17">
-        <v>46.07515549999997</v>
+        <v>45.97349919999996</v>
       </c>
       <c r="O17">
-        <v>13.82254664999999</v>
+        <v>13.79204975999999</v>
       </c>
       <c r="P17">
-        <v>32.25260884999997</v>
+        <v>32.18144943999997</v>
       </c>
       <c r="Q17">
-        <v>156.65260885</v>
+        <v>156.58144944</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1109104858744073</v>
+        <v>0.1114786402014091</v>
       </c>
       <c r="T17">
-        <v>0.5005316448795025</v>
+        <v>0.5048992857597774</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>31.21629779298805</v>
+        <v>29.2652791809263</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09927565776918366</v>
+        <v>0.09899590254512111</v>
       </c>
       <c r="C18">
-        <v>172.4564659164654</v>
+        <v>170.5571725433266</v>
       </c>
       <c r="D18">
-        <v>194.5924659164654</v>
+        <v>194.7141725433266</v>
       </c>
       <c r="E18">
-        <v>12.236</v>
+        <v>14.257</v>
       </c>
       <c r="F18">
-        <v>32.336</v>
+        <v>34.357</v>
       </c>
       <c r="G18">
         <v>10.2</v>
@@ -2763,28 +2763,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M18">
-        <v>1.6265008</v>
+        <v>1.7281571</v>
       </c>
       <c r="N18">
-        <v>45.97349919999996</v>
+        <v>45.87184289999997</v>
       </c>
       <c r="O18">
-        <v>13.79204975999999</v>
+        <v>13.76155286999999</v>
       </c>
       <c r="P18">
-        <v>32.18144943999997</v>
+        <v>32.11029002999998</v>
       </c>
       <c r="Q18">
-        <v>156.58144944</v>
+        <v>156.51029003</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1114786402014091</v>
+        <v>0.1120604849941218</v>
       </c>
       <c r="T18">
-        <v>0.5048992857597774</v>
+        <v>0.5093721709986132</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>29.2652791809263</v>
+        <v>27.54379217028358</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09899590254512111</v>
+        <v>0.09871614732105856</v>
       </c>
       <c r="C19">
-        <v>170.5571725433266</v>
+        <v>168.6580315067455</v>
       </c>
       <c r="D19">
-        <v>194.7141725433266</v>
+        <v>194.8360315067455</v>
       </c>
       <c r="E19">
-        <v>14.257</v>
+        <v>16.278</v>
       </c>
       <c r="F19">
-        <v>34.357</v>
+        <v>36.378</v>
       </c>
       <c r="G19">
         <v>10.2</v>
@@ -2845,28 +2845,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M19">
-        <v>1.7281571</v>
+        <v>1.8298134</v>
       </c>
       <c r="N19">
-        <v>45.87184289999997</v>
+        <v>45.77018659999997</v>
       </c>
       <c r="O19">
-        <v>13.76155286999999</v>
+        <v>13.73105597999999</v>
       </c>
       <c r="P19">
-        <v>32.11029002999998</v>
+        <v>32.03913061999998</v>
       </c>
       <c r="Q19">
-        <v>156.51029003</v>
+        <v>156.43913062</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1120604849941218</v>
+        <v>0.1126565211232421</v>
       </c>
       <c r="T19">
-        <v>0.5093721709986132</v>
+        <v>0.5139541509993717</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>27.54379217028358</v>
+        <v>26.01358149415671</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09871614732105857</v>
+        <v>0.09843639209699599</v>
       </c>
       <c r="C20">
-        <v>168.6580315067455</v>
+        <v>166.759043092914</v>
       </c>
       <c r="D20">
-        <v>194.8360315067455</v>
+        <v>194.958043092914</v>
       </c>
       <c r="E20">
-        <v>16.278</v>
+        <v>18.299</v>
       </c>
       <c r="F20">
-        <v>36.378</v>
+        <v>38.399</v>
       </c>
       <c r="G20">
         <v>10.2</v>
@@ -2927,28 +2927,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M20">
-        <v>1.8298134</v>
+        <v>1.9314697</v>
       </c>
       <c r="N20">
-        <v>45.77018659999997</v>
+        <v>45.66853029999996</v>
       </c>
       <c r="O20">
-        <v>13.73105597999999</v>
+        <v>13.70055908999999</v>
       </c>
       <c r="P20">
-        <v>32.03913061999998</v>
+        <v>31.96797120999997</v>
       </c>
       <c r="Q20">
-        <v>156.43913062</v>
+        <v>156.36797121</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1126565211232421</v>
+        <v>0.1132672741938222</v>
       </c>
       <c r="T20">
-        <v>0.5139541509993717</v>
+        <v>0.5186492663087909</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>26.01358149415671</v>
+        <v>24.6444456260432</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09843639209699599</v>
+        <v>0.09815663687293347</v>
       </c>
       <c r="C21">
-        <v>166.759043092914</v>
+        <v>164.860207588741</v>
       </c>
       <c r="D21">
-        <v>194.958043092914</v>
+        <v>195.080207588741</v>
       </c>
       <c r="E21">
-        <v>18.299</v>
+        <v>20.32</v>
       </c>
       <c r="F21">
-        <v>38.399</v>
+        <v>40.42</v>
       </c>
       <c r="G21">
         <v>10.2</v>
@@ -3009,28 +3009,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M21">
-        <v>1.9314697</v>
+        <v>2.033126</v>
       </c>
       <c r="N21">
-        <v>45.66853029999996</v>
+        <v>45.56687399999996</v>
       </c>
       <c r="O21">
-        <v>13.70055908999999</v>
+        <v>13.67006219999999</v>
       </c>
       <c r="P21">
-        <v>31.96797120999997</v>
+        <v>31.89681179999997</v>
       </c>
       <c r="Q21">
-        <v>156.36797121</v>
+        <v>156.2968118</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1132672741938222</v>
+        <v>0.1138932960911668</v>
       </c>
       <c r="T21">
-        <v>0.5186492663087909</v>
+        <v>0.5234617595009458</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>24.6444456260432</v>
+        <v>23.41222334474104</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09815663687293347</v>
+        <v>0.0978768816488709</v>
       </c>
       <c r="C22">
-        <v>164.860207588741</v>
+        <v>162.9615252818555</v>
       </c>
       <c r="D22">
-        <v>195.080207588741</v>
+        <v>195.2025252818555</v>
       </c>
       <c r="E22">
-        <v>20.32</v>
+        <v>22.341</v>
       </c>
       <c r="F22">
-        <v>40.42</v>
+        <v>42.441</v>
       </c>
       <c r="G22">
         <v>10.2</v>
@@ -3091,28 +3091,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M22">
-        <v>2.033126</v>
+        <v>2.1347823</v>
       </c>
       <c r="N22">
-        <v>45.56687399999996</v>
+        <v>45.46521769999997</v>
       </c>
       <c r="O22">
-        <v>13.67006219999999</v>
+        <v>13.63956530999999</v>
       </c>
       <c r="P22">
-        <v>31.89681179999997</v>
+        <v>31.82565238999998</v>
       </c>
       <c r="Q22">
-        <v>156.2968118</v>
+        <v>156.22565239</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1138932960911668</v>
+        <v>0.1145351666441404</v>
       </c>
       <c r="T22">
-        <v>0.5234617595009458</v>
+        <v>0.5283960879637879</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>23.41222334474104</v>
+        <v>22.29735556642004</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.0978768816488709</v>
+        <v>0.09759712642480832</v>
       </c>
       <c r="C23">
-        <v>162.9615252818555</v>
+        <v>161.0629964606078</v>
       </c>
       <c r="D23">
-        <v>195.2025252818555</v>
+        <v>195.3249964606078</v>
       </c>
       <c r="E23">
-        <v>22.34099999999999</v>
+        <v>24.36199999999999</v>
       </c>
       <c r="F23">
-        <v>42.441</v>
+        <v>44.462</v>
       </c>
       <c r="G23">
         <v>10.2</v>
@@ -3173,28 +3173,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M23">
-        <v>2.134782299999999</v>
+        <v>2.2364386</v>
       </c>
       <c r="N23">
-        <v>45.46521769999997</v>
+        <v>45.36356139999997</v>
       </c>
       <c r="O23">
-        <v>13.63956530999999</v>
+        <v>13.60906841999999</v>
       </c>
       <c r="P23">
-        <v>31.82565238999998</v>
+        <v>31.75449297999998</v>
       </c>
       <c r="Q23">
-        <v>156.22565239</v>
+        <v>156.15449298</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1145351666441404</v>
+        <v>0.1151934954164209</v>
       </c>
       <c r="T23">
-        <v>0.5283960879637879</v>
+        <v>0.5334569376692671</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>22.29735556642004</v>
+        <v>21.28383940431004</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09759712642480832</v>
+        <v>0.09731737120074578</v>
       </c>
       <c r="C24">
-        <v>161.0629964606078</v>
+        <v>159.1646214140727</v>
       </c>
       <c r="D24">
-        <v>195.3249964606078</v>
+        <v>195.4476214140728</v>
       </c>
       <c r="E24">
-        <v>24.36199999999999</v>
+        <v>26.383</v>
       </c>
       <c r="F24">
-        <v>44.462</v>
+        <v>46.483</v>
       </c>
       <c r="G24">
         <v>10.2</v>
@@ -3255,28 +3255,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M24">
-        <v>2.2364386</v>
+        <v>2.3380949</v>
       </c>
       <c r="N24">
-        <v>45.36356139999997</v>
+        <v>45.26190509999996</v>
       </c>
       <c r="O24">
-        <v>13.60906841999999</v>
+        <v>13.57857152999999</v>
       </c>
       <c r="P24">
-        <v>31.75449297999998</v>
+        <v>31.68333356999997</v>
       </c>
       <c r="Q24">
-        <v>156.15449298</v>
+        <v>156.08333357</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1151934954164209</v>
+        <v>0.1158689236373322</v>
       </c>
       <c r="T24">
-        <v>0.5334569376692671</v>
+        <v>0.5386492380164469</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>21.28383940431004</v>
+        <v>20.35845508238351</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09731737120074578</v>
+        <v>0.09703761597668324</v>
       </c>
       <c r="C25">
-        <v>159.1646214140727</v>
+        <v>157.2664004320513</v>
       </c>
       <c r="D25">
-        <v>195.4476214140728</v>
+        <v>195.5704004320513</v>
       </c>
       <c r="E25">
-        <v>26.383</v>
+        <v>28.404</v>
       </c>
       <c r="F25">
-        <v>46.483</v>
+        <v>48.504</v>
       </c>
       <c r="G25">
         <v>10.2</v>
@@ -3337,28 +3337,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M25">
-        <v>2.3380949</v>
+        <v>2.4397512</v>
       </c>
       <c r="N25">
-        <v>45.26190509999996</v>
+        <v>45.16024879999996</v>
       </c>
       <c r="O25">
-        <v>13.57857152999999</v>
+        <v>13.54807463999999</v>
       </c>
       <c r="P25">
-        <v>31.68333356999997</v>
+        <v>31.61217415999997</v>
       </c>
       <c r="Q25">
-        <v>156.08333357</v>
+        <v>156.01217416</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1158689236373322</v>
+        <v>0.1165621262851095</v>
       </c>
       <c r="T25">
-        <v>0.5386492380164469</v>
+        <v>0.5439781778464475</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>20.35845508238351</v>
+        <v>19.51018612061753</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09703761597668324</v>
+        <v>0.09675786075262068</v>
       </c>
       <c r="C26">
-        <v>157.2664004320513</v>
+        <v>155.3683338050731</v>
       </c>
       <c r="D26">
-        <v>195.5704004320513</v>
+        <v>195.6933338050732</v>
       </c>
       <c r="E26">
-        <v>28.404</v>
+        <v>30.425</v>
       </c>
       <c r="F26">
-        <v>48.504</v>
+        <v>50.525</v>
       </c>
       <c r="G26">
         <v>10.2</v>
@@ -3419,28 +3419,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M26">
-        <v>2.4397512</v>
+        <v>2.5414075</v>
       </c>
       <c r="N26">
-        <v>45.16024879999996</v>
+        <v>45.05859249999997</v>
       </c>
       <c r="O26">
-        <v>13.54807463999999</v>
+        <v>13.51757774999999</v>
       </c>
       <c r="P26">
-        <v>31.61217415999997</v>
+        <v>31.54101474999998</v>
       </c>
       <c r="Q26">
-        <v>156.01217416</v>
+        <v>155.94101475</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1165621262851095</v>
+        <v>0.1172738143368276</v>
       </c>
       <c r="T26">
-        <v>0.5439781778464475</v>
+        <v>0.5494492227385813</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>19.51018612061753</v>
+        <v>18.72977867579283</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09675786075262068</v>
+        <v>0.09647810552855812</v>
       </c>
       <c r="C27">
-        <v>155.3683338050731</v>
+        <v>153.470421824399</v>
       </c>
       <c r="D27">
-        <v>195.6933338050732</v>
+        <v>195.816421824399</v>
       </c>
       <c r="E27">
-        <v>30.425</v>
+        <v>32.446</v>
       </c>
       <c r="F27">
-        <v>50.525</v>
+        <v>52.546</v>
       </c>
       <c r="G27">
         <v>10.2</v>
@@ -3501,28 +3501,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M27">
-        <v>2.5414075</v>
+        <v>2.6430638</v>
       </c>
       <c r="N27">
-        <v>45.05859249999997</v>
+        <v>44.95693619999997</v>
       </c>
       <c r="O27">
-        <v>13.51757774999999</v>
+        <v>13.48708085999999</v>
       </c>
       <c r="P27">
-        <v>31.54101474999998</v>
+        <v>31.46985533999997</v>
       </c>
       <c r="Q27">
-        <v>155.94101475</v>
+        <v>155.86985534</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1172738143368276</v>
+        <v>0.1180047372007542</v>
       </c>
       <c r="T27">
-        <v>0.5494492227385813</v>
+        <v>0.5550681337088809</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>18.72977867579283</v>
+        <v>18.00940257287772</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09647810552855812</v>
+        <v>0.09619835030449558</v>
       </c>
       <c r="C28">
-        <v>153.470421824399</v>
+        <v>151.5726647820228</v>
       </c>
       <c r="D28">
-        <v>195.816421824399</v>
+        <v>195.9396647820228</v>
       </c>
       <c r="E28">
-        <v>32.446</v>
+        <v>34.467</v>
       </c>
       <c r="F28">
-        <v>52.546</v>
+        <v>54.567</v>
       </c>
       <c r="G28">
         <v>10.2</v>
@@ -3583,28 +3583,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M28">
-        <v>2.6430638</v>
+        <v>2.7447201</v>
       </c>
       <c r="N28">
-        <v>44.95693619999997</v>
+        <v>44.85527989999996</v>
       </c>
       <c r="O28">
-        <v>13.48708085999999</v>
+        <v>13.45658396999999</v>
       </c>
       <c r="P28">
-        <v>31.46985533999997</v>
+        <v>31.39869592999997</v>
       </c>
       <c r="Q28">
-        <v>155.86985534</v>
+        <v>155.79869593</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1180047372007542</v>
+        <v>0.1187556853486241</v>
       </c>
       <c r="T28">
-        <v>0.5550681337088809</v>
+        <v>0.56084098744549</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>18.00940257287772</v>
+        <v>17.34238766277114</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09619835030449558</v>
+        <v>0.09591859508043302</v>
       </c>
       <c r="C29">
-        <v>151.5726647820228</v>
+        <v>149.675062970674</v>
       </c>
       <c r="D29">
-        <v>195.9396647820228</v>
+        <v>196.063062970674</v>
       </c>
       <c r="E29">
-        <v>34.467</v>
+        <v>36.488</v>
       </c>
       <c r="F29">
-        <v>54.567</v>
+        <v>56.588</v>
       </c>
       <c r="G29">
         <v>10.2</v>
@@ -3665,28 +3665,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M29">
-        <v>2.7447201</v>
+        <v>2.8463764</v>
       </c>
       <c r="N29">
-        <v>44.85527989999996</v>
+        <v>44.75362359999997</v>
       </c>
       <c r="O29">
-        <v>13.45658396999999</v>
+        <v>13.42608707999999</v>
       </c>
       <c r="P29">
-        <v>31.39869592999997</v>
+        <v>31.32753651999998</v>
       </c>
       <c r="Q29">
-        <v>155.79869593</v>
+        <v>155.72753652</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1187556853486241</v>
+        <v>0.1195274931672681</v>
       </c>
       <c r="T29">
-        <v>0.56084098744549</v>
+        <v>0.5667741982303384</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>17.34238766277114</v>
+        <v>16.72301667481503</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09591859508043302</v>
+        <v>0.09563883985637046</v>
       </c>
       <c r="C30">
-        <v>149.675062970674</v>
+        <v>147.7776166838199</v>
       </c>
       <c r="D30">
-        <v>196.063062970674</v>
+        <v>196.1866166838199</v>
       </c>
       <c r="E30">
-        <v>36.488</v>
+        <v>38.50900000000001</v>
       </c>
       <c r="F30">
-        <v>56.588</v>
+        <v>58.60900000000001</v>
       </c>
       <c r="G30">
         <v>10.2</v>
@@ -3747,28 +3747,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M30">
-        <v>2.8463764</v>
+        <v>2.9480327</v>
       </c>
       <c r="N30">
-        <v>44.75362359999997</v>
+        <v>44.65196729999997</v>
       </c>
       <c r="O30">
-        <v>13.42608707999999</v>
+        <v>13.39559018999999</v>
       </c>
       <c r="P30">
-        <v>31.32753651999998</v>
+        <v>31.25637710999998</v>
       </c>
       <c r="Q30">
-        <v>155.72753652</v>
+        <v>155.65637711</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1195274931672681</v>
+        <v>0.120321042051226</v>
       </c>
       <c r="T30">
-        <v>0.5667741982303384</v>
+        <v>0.5728745417133514</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>16.72301667481503</v>
+        <v>16.14636092740761</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09563883985637046</v>
+        <v>0.09535908463230791</v>
       </c>
       <c r="C31">
-        <v>147.7776166838199</v>
+        <v>145.8803262156681</v>
       </c>
       <c r="D31">
-        <v>196.1866166838199</v>
+        <v>196.3103262156681</v>
       </c>
       <c r="E31">
-        <v>38.50899999999999</v>
+        <v>40.52999999999999</v>
       </c>
       <c r="F31">
-        <v>58.60899999999999</v>
+        <v>60.63</v>
       </c>
       <c r="G31">
         <v>10.2</v>
@@ -3829,28 +3829,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M31">
-        <v>2.9480327</v>
+        <v>3.049688999999999</v>
       </c>
       <c r="N31">
-        <v>44.65196729999997</v>
+        <v>44.55031099999997</v>
       </c>
       <c r="O31">
-        <v>13.39559018999999</v>
+        <v>13.36509329999999</v>
       </c>
       <c r="P31">
-        <v>31.25637710999998</v>
+        <v>31.18521769999997</v>
       </c>
       <c r="Q31">
-        <v>155.65637711</v>
+        <v>155.5852177</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.120321042051226</v>
+        <v>0.1211372637604399</v>
       </c>
       <c r="T31">
-        <v>0.5728745417133514</v>
+        <v>0.5791491807244505</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>16.14636092740761</v>
+        <v>15.60814889649403</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09535908463230791</v>
+        <v>0.09507932940824534</v>
       </c>
       <c r="C32">
-        <v>145.8803262156681</v>
+        <v>143.9831918611687</v>
       </c>
       <c r="D32">
-        <v>196.3103262156681</v>
+        <v>196.4341918611688</v>
       </c>
       <c r="E32">
-        <v>40.52999999999999</v>
+        <v>42.55099999999999</v>
       </c>
       <c r="F32">
-        <v>60.63</v>
+        <v>62.651</v>
       </c>
       <c r="G32">
         <v>10.2</v>
@@ -3911,28 +3911,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M32">
-        <v>3.049688999999999</v>
+        <v>3.1513453</v>
       </c>
       <c r="N32">
-        <v>44.55031099999997</v>
+        <v>44.44865469999996</v>
       </c>
       <c r="O32">
-        <v>13.36509329999999</v>
+        <v>13.33459640999999</v>
       </c>
       <c r="P32">
-        <v>31.18521769999997</v>
+        <v>31.11405828999997</v>
       </c>
       <c r="Q32">
-        <v>155.5852177</v>
+        <v>155.51405829</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1211372637604399</v>
+        <v>0.1219771440699208</v>
       </c>
       <c r="T32">
-        <v>0.5791491807244505</v>
+        <v>0.5856056933300743</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>15.60814889649403</v>
+        <v>15.10466022241357</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09507932940824534</v>
+        <v>0.09479957418418281</v>
       </c>
       <c r="C33">
-        <v>143.9831918611687</v>
+        <v>142.0862139160168</v>
       </c>
       <c r="D33">
-        <v>196.4341918611688</v>
+        <v>196.5582139160168</v>
       </c>
       <c r="E33">
-        <v>42.55099999999999</v>
+        <v>44.572</v>
       </c>
       <c r="F33">
-        <v>62.651</v>
+        <v>64.672</v>
       </c>
       <c r="G33">
         <v>10.2</v>
@@ -3993,28 +3993,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M33">
-        <v>3.1513453</v>
+        <v>3.2530016</v>
       </c>
       <c r="N33">
-        <v>44.44865469999996</v>
+        <v>44.34699839999997</v>
       </c>
       <c r="O33">
-        <v>13.33459640999999</v>
+        <v>13.30409951999999</v>
       </c>
       <c r="P33">
-        <v>31.11405828999997</v>
+        <v>31.04289887999998</v>
       </c>
       <c r="Q33">
-        <v>155.51405829</v>
+        <v>155.44289888</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1219771440699208</v>
+        <v>0.1228417267414453</v>
       </c>
       <c r="T33">
-        <v>0.5856056933300743</v>
+        <v>0.5922521033652752</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>15.10466022241357</v>
+        <v>14.63263959046315</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09479957418418281</v>
+        <v>0.09451981896012024</v>
       </c>
       <c r="C34">
-        <v>142.0862139160168</v>
+        <v>140.1893926766546</v>
       </c>
       <c r="D34">
-        <v>196.5582139160168</v>
+        <v>196.6823926766546</v>
       </c>
       <c r="E34">
-        <v>44.572</v>
+        <v>46.593</v>
       </c>
       <c r="F34">
-        <v>64.672</v>
+        <v>66.693</v>
       </c>
       <c r="G34">
         <v>10.2</v>
@@ -4075,28 +4075,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M34">
-        <v>3.2530016</v>
+        <v>3.3546579</v>
       </c>
       <c r="N34">
-        <v>44.34699839999997</v>
+        <v>44.24534209999997</v>
       </c>
       <c r="O34">
-        <v>13.30409951999999</v>
+        <v>13.27360262999999</v>
       </c>
       <c r="P34">
-        <v>31.04289887999998</v>
+        <v>30.97173946999997</v>
       </c>
       <c r="Q34">
-        <v>155.44289888</v>
+        <v>155.37173947</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1228417267414453</v>
+        <v>0.1237321178509257</v>
       </c>
       <c r="T34">
-        <v>0.5922521033652752</v>
+        <v>0.5990969137000345</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>14.63263959046315</v>
+        <v>14.18922626954002</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09451981896012024</v>
+        <v>0.0942400637360577</v>
       </c>
       <c r="C35">
-        <v>140.1893926766546</v>
+        <v>138.2927284402737</v>
       </c>
       <c r="D35">
-        <v>196.6823926766546</v>
+        <v>196.8067284402738</v>
       </c>
       <c r="E35">
-        <v>46.593</v>
+        <v>48.614</v>
       </c>
       <c r="F35">
-        <v>66.693</v>
+        <v>68.714</v>
       </c>
       <c r="G35">
         <v>10.2</v>
@@ -4157,28 +4157,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M35">
-        <v>3.3546579</v>
+        <v>3.4563142</v>
       </c>
       <c r="N35">
-        <v>44.24534209999997</v>
+        <v>44.14368579999996</v>
       </c>
       <c r="O35">
-        <v>13.27360262999999</v>
+        <v>13.24310573999999</v>
       </c>
       <c r="P35">
-        <v>30.97173946999997</v>
+        <v>30.90058005999997</v>
       </c>
       <c r="Q35">
-        <v>155.37173947</v>
+        <v>155.30058006</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1237321178509257</v>
+        <v>0.1246494905091783</v>
       </c>
       <c r="T35">
-        <v>0.5990969137000345</v>
+        <v>0.6061491425297862</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>14.18922626954002</v>
+        <v>13.77189608514179</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0942400637360577</v>
+        <v>0.09396030851199513</v>
       </c>
       <c r="C36">
-        <v>138.2927284402737</v>
+        <v>136.3962215048183</v>
       </c>
       <c r="D36">
-        <v>196.8067284402738</v>
+        <v>196.9312215048183</v>
       </c>
       <c r="E36">
-        <v>48.614</v>
+        <v>50.635</v>
       </c>
       <c r="F36">
-        <v>68.714</v>
+        <v>70.735</v>
       </c>
       <c r="G36">
         <v>10.2</v>
@@ -4239,28 +4239,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M36">
-        <v>3.4563142</v>
+        <v>3.5579705</v>
       </c>
       <c r="N36">
-        <v>44.14368579999996</v>
+        <v>44.04202949999997</v>
       </c>
       <c r="O36">
-        <v>13.24310573999999</v>
+        <v>13.21260884999999</v>
       </c>
       <c r="P36">
-        <v>30.90058005999997</v>
+        <v>30.82942064999998</v>
       </c>
       <c r="Q36">
-        <v>155.30058006</v>
+        <v>155.22942065</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1246494905091783</v>
+        <v>0.1255950900184541</v>
       </c>
       <c r="T36">
-        <v>0.6061491425297862</v>
+        <v>0.6134183630158382</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>13.77189608514179</v>
+        <v>13.37841333985202</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09396030851199513</v>
+        <v>0.09368055328793258</v>
       </c>
       <c r="C37">
-        <v>136.3962215048183</v>
+        <v>134.4998721689863</v>
       </c>
       <c r="D37">
-        <v>196.9312215048183</v>
+        <v>197.0558721689863</v>
       </c>
       <c r="E37">
-        <v>50.635</v>
+        <v>52.656</v>
       </c>
       <c r="F37">
-        <v>70.735</v>
+        <v>72.756</v>
       </c>
       <c r="G37">
         <v>10.2</v>
@@ -4321,28 +4321,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M37">
-        <v>3.5579705</v>
+        <v>3.6596268</v>
       </c>
       <c r="N37">
-        <v>44.04202949999997</v>
+        <v>43.94037319999997</v>
       </c>
       <c r="O37">
-        <v>13.21260884999999</v>
+        <v>13.18211195999999</v>
       </c>
       <c r="P37">
-        <v>30.82942064999998</v>
+        <v>30.75826123999998</v>
       </c>
       <c r="Q37">
-        <v>155.22942065</v>
+        <v>155.15826124</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1255950900184541</v>
+        <v>0.1265702395123947</v>
       </c>
       <c r="T37">
-        <v>0.6134183630158382</v>
+        <v>0.6209147466420792</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>13.37841333985202</v>
+        <v>13.00679074707836</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09368055328793259</v>
+        <v>0.09378929806387004</v>
       </c>
       <c r="C38">
-        <v>134.4998721689863</v>
+        <v>132.4303999658917</v>
       </c>
       <c r="D38">
-        <v>197.0558721689863</v>
+        <v>197.0073999658917</v>
       </c>
       <c r="E38">
-        <v>52.656</v>
+        <v>54.677</v>
       </c>
       <c r="F38">
-        <v>72.756</v>
+        <v>74.777</v>
       </c>
       <c r="G38">
         <v>10.2</v>
@@ -4403,45 +4403,45 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M38">
-        <v>3.6596268</v>
+        <v>3.8734486</v>
       </c>
       <c r="N38">
-        <v>43.94037319999997</v>
+        <v>43.72655139999996</v>
       </c>
       <c r="O38">
-        <v>13.18211195999999</v>
+        <v>13.11796541999999</v>
       </c>
       <c r="P38">
-        <v>30.75826123999998</v>
+        <v>30.60858597999997</v>
       </c>
       <c r="Q38">
-        <v>155.15826124</v>
+        <v>155.00858598</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1265702395123947</v>
+        <v>0.127576346133127</v>
       </c>
       <c r="T38">
-        <v>0.6209147466420792</v>
+        <v>0.6286491107008992</v>
       </c>
       <c r="U38">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y38">
-        <v>13.00679074707836</v>
+        <v>12.28879092393274</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09378929806387004</v>
+        <v>0.09352004283980747</v>
       </c>
       <c r="C39">
-        <v>132.4303999658917</v>
+        <v>130.5294621512826</v>
       </c>
       <c r="D39">
-        <v>197.0073999658917</v>
+        <v>197.1274621512826</v>
       </c>
       <c r="E39">
-        <v>54.677</v>
+        <v>56.698</v>
       </c>
       <c r="F39">
-        <v>74.777</v>
+        <v>76.798</v>
       </c>
       <c r="G39">
         <v>10.2</v>
@@ -4485,28 +4485,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M39">
-        <v>3.8734486</v>
+        <v>3.9781364</v>
       </c>
       <c r="N39">
-        <v>43.72655139999996</v>
+        <v>43.62186359999997</v>
       </c>
       <c r="O39">
-        <v>13.11796541999999</v>
+        <v>13.08655907999999</v>
       </c>
       <c r="P39">
-        <v>30.60858597999997</v>
+        <v>30.53530451999998</v>
       </c>
       <c r="Q39">
-        <v>155.00858598</v>
+        <v>154.93530452</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.127576346133127</v>
+        <v>0.1286149078061411</v>
       </c>
       <c r="T39">
-        <v>0.6286491107008992</v>
+        <v>0.63663297037452</v>
       </c>
       <c r="U39">
         <v>0.0518</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>12.28879092393274</v>
+        <v>11.9654016890924</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09352004283980747</v>
+        <v>0.09325078761574493</v>
       </c>
       <c r="C40">
-        <v>130.5294621512826</v>
+        <v>128.6286707648645</v>
       </c>
       <c r="D40">
-        <v>197.1274621512826</v>
+        <v>197.2476707648645</v>
       </c>
       <c r="E40">
-        <v>56.698</v>
+        <v>58.719</v>
       </c>
       <c r="F40">
-        <v>76.798</v>
+        <v>78.819</v>
       </c>
       <c r="G40">
         <v>10.2</v>
@@ -4567,28 +4567,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M40">
-        <v>3.9781364</v>
+        <v>4.0828242</v>
       </c>
       <c r="N40">
-        <v>43.62186359999997</v>
+        <v>43.51717579999997</v>
       </c>
       <c r="O40">
-        <v>13.08655907999999</v>
+        <v>13.05515273999999</v>
       </c>
       <c r="P40">
-        <v>30.53530451999998</v>
+        <v>30.46202305999998</v>
       </c>
       <c r="Q40">
-        <v>154.93530452</v>
+        <v>154.86202306</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1286149078061411</v>
+        <v>0.1296875206815491</v>
       </c>
       <c r="T40">
-        <v>0.63663297037452</v>
+        <v>0.6448785959390793</v>
       </c>
       <c r="U40">
         <v>0.0518</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>11.9654016890924</v>
+        <v>11.65859651757721</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09325078761574493</v>
+        <v>0.09298153239168239</v>
       </c>
       <c r="C41">
-        <v>128.6286707648645</v>
+        <v>126.7280260746772</v>
       </c>
       <c r="D41">
-        <v>197.2476707648645</v>
+        <v>197.3680260746772</v>
       </c>
       <c r="E41">
-        <v>58.719</v>
+        <v>60.74</v>
       </c>
       <c r="F41">
-        <v>78.819</v>
+        <v>80.84</v>
       </c>
       <c r="G41">
         <v>10.2</v>
@@ -4649,28 +4649,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M41">
-        <v>4.0828242</v>
+        <v>4.187512</v>
       </c>
       <c r="N41">
-        <v>43.51717579999997</v>
+        <v>43.41248799999997</v>
       </c>
       <c r="O41">
-        <v>13.05515273999999</v>
+        <v>13.02374639999999</v>
       </c>
       <c r="P41">
-        <v>30.46202305999998</v>
+        <v>30.38874159999998</v>
       </c>
       <c r="Q41">
-        <v>154.86202306</v>
+        <v>154.7887416</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1296875206815491</v>
+        <v>0.1307958873194706</v>
       </c>
       <c r="T41">
-        <v>0.6448785959390793</v>
+        <v>0.6533990756891238</v>
       </c>
       <c r="U41">
         <v>0.0518</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>11.65859651757721</v>
+        <v>11.36713160463778</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09298153239168239</v>
+        <v>0.0927122771676198</v>
       </c>
       <c r="C42">
-        <v>126.7280260746772</v>
+        <v>124.8275283494154</v>
       </c>
       <c r="D42">
-        <v>197.3680260746772</v>
+        <v>197.4885283494154</v>
       </c>
       <c r="E42">
-        <v>60.74</v>
+        <v>62.761</v>
       </c>
       <c r="F42">
-        <v>80.84</v>
+        <v>82.861</v>
       </c>
       <c r="G42">
         <v>10.2</v>
@@ -4731,28 +4731,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M42">
-        <v>4.187512</v>
+        <v>4.2921998</v>
       </c>
       <c r="N42">
-        <v>43.41248799999997</v>
+        <v>43.30780019999997</v>
       </c>
       <c r="O42">
-        <v>13.02374639999999</v>
+        <v>12.99234005999999</v>
       </c>
       <c r="P42">
-        <v>30.38874159999998</v>
+        <v>30.31546013999998</v>
       </c>
       <c r="Q42">
-        <v>154.7887416</v>
+        <v>154.71546014</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1307958873194706</v>
+        <v>0.1319418257078302</v>
       </c>
       <c r="T42">
-        <v>0.6533990756891238</v>
+        <v>0.6622083852612035</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>11.36713160463778</v>
+        <v>11.08988449232954</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0927122771676198</v>
+        <v>0.09244302194355726</v>
       </c>
       <c r="C43">
-        <v>124.8275283494154</v>
+        <v>122.92717785843</v>
       </c>
       <c r="D43">
-        <v>197.4885283494154</v>
+        <v>197.60917785843</v>
       </c>
       <c r="E43">
-        <v>62.761</v>
+        <v>64.78200000000001</v>
       </c>
       <c r="F43">
-        <v>82.861</v>
+        <v>84.88200000000001</v>
       </c>
       <c r="G43">
         <v>10.2</v>
@@ -4813,28 +4813,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M43">
-        <v>4.2921998</v>
+        <v>4.3968876</v>
       </c>
       <c r="N43">
-        <v>43.30780019999997</v>
+        <v>43.20311239999997</v>
       </c>
       <c r="O43">
-        <v>12.99234005999999</v>
+        <v>12.96093371999999</v>
       </c>
       <c r="P43">
-        <v>30.31546013999998</v>
+        <v>30.24217867999998</v>
       </c>
       <c r="Q43">
-        <v>154.71546014</v>
+        <v>154.64217868</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1319418257078302</v>
+        <v>0.1331272792130298</v>
       </c>
       <c r="T43">
-        <v>0.6622083852612035</v>
+        <v>0.6713214641288724</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.08988449232954</v>
+        <v>10.82583962346455</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09244302194355726</v>
+        <v>0.09217376671949472</v>
       </c>
       <c r="C44">
-        <v>122.92717785843</v>
+        <v>121.0269748717305</v>
       </c>
       <c r="D44">
-        <v>197.60917785843</v>
+        <v>197.7299748717305</v>
       </c>
       <c r="E44">
-        <v>64.78199999999998</v>
+        <v>66.803</v>
       </c>
       <c r="F44">
-        <v>84.88199999999999</v>
+        <v>86.90299999999999</v>
       </c>
       <c r="G44">
         <v>10.2</v>
@@ -4895,28 +4895,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M44">
-        <v>4.396887599999999</v>
+        <v>4.501575399999999</v>
       </c>
       <c r="N44">
-        <v>43.20311239999997</v>
+        <v>43.09842459999997</v>
       </c>
       <c r="O44">
-        <v>12.96093371999999</v>
+        <v>12.92952737999999</v>
       </c>
       <c r="P44">
-        <v>30.24217867999998</v>
+        <v>30.16889721999998</v>
       </c>
       <c r="Q44">
-        <v>154.64217868</v>
+        <v>154.56889722</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1331272792130297</v>
+        <v>0.1343543275780609</v>
       </c>
       <c r="T44">
-        <v>0.6713214641288723</v>
+        <v>0.6807543001497927</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>10.82583962346455</v>
+        <v>10.57407591129096</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09217376671949472</v>
+        <v>0.09190451149543215</v>
       </c>
       <c r="C45">
-        <v>121.0269748717305</v>
+        <v>119.1269196599874</v>
       </c>
       <c r="D45">
-        <v>197.7299748717305</v>
+        <v>197.8509196599874</v>
       </c>
       <c r="E45">
-        <v>66.803</v>
+        <v>68.82399999999998</v>
       </c>
       <c r="F45">
-        <v>86.90299999999999</v>
+        <v>88.92399999999999</v>
       </c>
       <c r="G45">
         <v>10.2</v>
@@ -4977,28 +4977,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M45">
-        <v>4.501575399999999</v>
+        <v>4.6062632</v>
       </c>
       <c r="N45">
-        <v>43.09842459999997</v>
+        <v>42.99373679999997</v>
       </c>
       <c r="O45">
-        <v>12.92952737999999</v>
+        <v>12.89812103999999</v>
       </c>
       <c r="P45">
-        <v>30.16889721999998</v>
+        <v>30.09561575999998</v>
       </c>
       <c r="Q45">
-        <v>154.56889722</v>
+        <v>154.49561576</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1343543275780609</v>
+        <v>0.135625199098986</v>
       </c>
       <c r="T45">
-        <v>0.6807543001497927</v>
+        <v>0.6905240231714602</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>10.57407591129096</v>
+        <v>10.33375600421616</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09190451149543215</v>
+        <v>0.09163525627136961</v>
       </c>
       <c r="C46">
-        <v>119.1269196599874</v>
+        <v>117.2270124945334</v>
       </c>
       <c r="D46">
-        <v>197.8509196599874</v>
+        <v>197.9720124945334</v>
       </c>
       <c r="E46">
-        <v>68.82399999999998</v>
+        <v>70.845</v>
       </c>
       <c r="F46">
-        <v>88.92399999999999</v>
+        <v>90.94499999999999</v>
       </c>
       <c r="G46">
         <v>10.2</v>
@@ -5059,28 +5059,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M46">
-        <v>4.6062632</v>
+        <v>4.710951</v>
       </c>
       <c r="N46">
-        <v>42.99373679999997</v>
+        <v>42.88904899999996</v>
       </c>
       <c r="O46">
-        <v>12.89812103999999</v>
+        <v>12.86671469999999</v>
       </c>
       <c r="P46">
-        <v>30.09561575999998</v>
+        <v>30.02233429999998</v>
       </c>
       <c r="Q46">
-        <v>154.49561576</v>
+        <v>154.4223343</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.135625199098986</v>
+        <v>0.1369422841297629</v>
       </c>
       <c r="T46">
-        <v>0.6905240231714602</v>
+        <v>0.7006490088484612</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>10.33375600421616</v>
+        <v>10.10411698190025</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09163525627136961</v>
+        <v>0.09136600104730706</v>
       </c>
       <c r="C47">
-        <v>117.2270124945334</v>
+        <v>115.3272536473661</v>
       </c>
       <c r="D47">
-        <v>197.9720124945334</v>
+        <v>198.0932536473662</v>
       </c>
       <c r="E47">
-        <v>70.845</v>
+        <v>72.86600000000001</v>
       </c>
       <c r="F47">
-        <v>90.94499999999999</v>
+        <v>92.96600000000001</v>
       </c>
       <c r="G47">
         <v>10.2</v>
@@ -5141,28 +5141,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M47">
-        <v>4.710951</v>
+        <v>4.8156388</v>
       </c>
       <c r="N47">
-        <v>42.88904899999996</v>
+        <v>42.78436119999996</v>
       </c>
       <c r="O47">
-        <v>12.86671469999999</v>
+        <v>12.83530835999999</v>
       </c>
       <c r="P47">
-        <v>30.02233429999998</v>
+        <v>29.94905283999998</v>
       </c>
       <c r="Q47">
-        <v>154.4223343</v>
+        <v>154.34905284</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1369422841297629</v>
+        <v>0.1383081500876057</v>
       </c>
       <c r="T47">
-        <v>0.7006490088484612</v>
+        <v>0.7111489939949805</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.10411698190025</v>
+        <v>9.884462264902417</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09136600104730706</v>
+        <v>0.09165604582324452</v>
       </c>
       <c r="C48">
-        <v>115.3272536473661</v>
+        <v>113.1756574763263</v>
       </c>
       <c r="D48">
-        <v>198.0932536473662</v>
+        <v>197.9626574763263</v>
       </c>
       <c r="E48">
-        <v>72.86600000000001</v>
+        <v>74.887</v>
       </c>
       <c r="F48">
-        <v>92.96600000000001</v>
+        <v>94.98700000000001</v>
       </c>
       <c r="G48">
         <v>10.2</v>
@@ -5223,45 +5223,45 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M48">
-        <v>4.8156388</v>
+        <v>5.081804500000001</v>
       </c>
       <c r="N48">
-        <v>42.78436119999996</v>
+        <v>42.51819549999996</v>
       </c>
       <c r="O48">
-        <v>12.83530835999999</v>
+        <v>12.75545864999999</v>
       </c>
       <c r="P48">
-        <v>29.94905283999998</v>
+        <v>29.76273684999997</v>
       </c>
       <c r="Q48">
-        <v>154.34905284</v>
+        <v>154.16273685</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1383081500876057</v>
+        <v>0.1397255581570651</v>
       </c>
       <c r="T48">
-        <v>0.7111489939949805</v>
+        <v>0.7220452049960857</v>
       </c>
       <c r="U48">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V48">
         <v>0.3</v>
       </c>
       <c r="W48">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y48">
-        <v>9.884462264902417</v>
+        <v>9.366751515136002</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09165604582324452</v>
+        <v>0.09139869059918196</v>
       </c>
       <c r="C49">
-        <v>113.1756574763263</v>
+        <v>111.2705261659256</v>
       </c>
       <c r="D49">
-        <v>197.9626574763263</v>
+        <v>198.0785261659256</v>
       </c>
       <c r="E49">
-        <v>74.887</v>
+        <v>76.90800000000002</v>
       </c>
       <c r="F49">
-        <v>94.98700000000001</v>
+        <v>97.00800000000001</v>
       </c>
       <c r="G49">
         <v>10.2</v>
@@ -5305,28 +5305,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M49">
-        <v>5.081804500000001</v>
+        <v>5.189928</v>
       </c>
       <c r="N49">
-        <v>42.51819549999996</v>
+        <v>42.41007199999996</v>
       </c>
       <c r="O49">
-        <v>12.75545864999999</v>
+        <v>12.72302159999999</v>
       </c>
       <c r="P49">
-        <v>29.76273684999997</v>
+        <v>29.68705039999998</v>
       </c>
       <c r="Q49">
-        <v>154.16273685</v>
+        <v>154.0870504</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1397255581570651</v>
+        <v>0.1411974819215037</v>
       </c>
       <c r="T49">
-        <v>0.7220452049960857</v>
+        <v>0.7333605010356947</v>
       </c>
       <c r="U49">
         <v>0.0535</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>9.366751515136002</v>
+        <v>9.17161085857067</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09139869059918196</v>
+        <v>0.09114133537511937</v>
       </c>
       <c r="C50">
-        <v>111.2705261659256</v>
+        <v>109.3655305721905</v>
       </c>
       <c r="D50">
-        <v>198.0785261659256</v>
+        <v>198.1945305721905</v>
       </c>
       <c r="E50">
-        <v>76.90799999999999</v>
+        <v>78.929</v>
       </c>
       <c r="F50">
-        <v>97.008</v>
+        <v>99.029</v>
       </c>
       <c r="G50">
         <v>10.2</v>
@@ -5387,28 +5387,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M50">
-        <v>5.189928</v>
+        <v>5.2980515</v>
       </c>
       <c r="N50">
-        <v>42.41007199999996</v>
+        <v>42.30194849999997</v>
       </c>
       <c r="O50">
-        <v>12.72302159999999</v>
+        <v>12.69058454999999</v>
       </c>
       <c r="P50">
-        <v>29.68705039999998</v>
+        <v>29.61136394999998</v>
       </c>
       <c r="Q50">
-        <v>154.0870504</v>
+        <v>154.01136395</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1411974819215037</v>
+        <v>0.1427271281865086</v>
       </c>
       <c r="T50">
-        <v>0.7333605010356947</v>
+        <v>0.7451195341748963</v>
       </c>
       <c r="U50">
         <v>0.0535</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>9.17161085857067</v>
+        <v>8.984435126763106</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09114133537511937</v>
+        <v>0.09088398015105684</v>
       </c>
       <c r="C51">
-        <v>109.3655305721905</v>
+        <v>107.4606709337074</v>
       </c>
       <c r="D51">
-        <v>198.1945305721905</v>
+        <v>198.3106709337074</v>
       </c>
       <c r="E51">
-        <v>78.929</v>
+        <v>80.94999999999999</v>
       </c>
       <c r="F51">
-        <v>99.029</v>
+        <v>101.05</v>
       </c>
       <c r="G51">
         <v>10.2</v>
@@ -5469,28 +5469,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M51">
-        <v>5.2980515</v>
+        <v>5.406175</v>
       </c>
       <c r="N51">
-        <v>42.30194849999997</v>
+        <v>42.19382499999997</v>
       </c>
       <c r="O51">
-        <v>12.69058454999999</v>
+        <v>12.65814749999999</v>
       </c>
       <c r="P51">
-        <v>29.61136394999998</v>
+        <v>29.53567749999998</v>
       </c>
       <c r="Q51">
-        <v>154.01136395</v>
+        <v>153.9356775</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1427271281865086</v>
+        <v>0.1443179603021137</v>
       </c>
       <c r="T51">
-        <v>0.7451195341748963</v>
+        <v>0.7573489286396661</v>
       </c>
       <c r="U51">
         <v>0.0535</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.984435126763106</v>
+        <v>8.804746424227844</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09088398015105684</v>
+        <v>0.09062662492699428</v>
       </c>
       <c r="C52">
-        <v>107.4606709337074</v>
+        <v>105.5559474896225</v>
       </c>
       <c r="D52">
-        <v>198.3106709337074</v>
+        <v>198.4269474896225</v>
       </c>
       <c r="E52">
-        <v>80.94999999999999</v>
+        <v>82.971</v>
       </c>
       <c r="F52">
-        <v>101.05</v>
+        <v>103.071</v>
       </c>
       <c r="G52">
         <v>10.2</v>
@@ -5551,28 +5551,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M52">
-        <v>5.406175</v>
+        <v>5.5142985</v>
       </c>
       <c r="N52">
-        <v>42.19382499999997</v>
+        <v>42.08570149999996</v>
       </c>
       <c r="O52">
-        <v>12.65814749999999</v>
+        <v>12.62571044999999</v>
       </c>
       <c r="P52">
-        <v>29.53567749999998</v>
+        <v>29.45999104999997</v>
       </c>
       <c r="Q52">
-        <v>153.9356775</v>
+        <v>153.85999105</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1443179603021137</v>
+        <v>0.1459737243408047</v>
       </c>
       <c r="T52">
-        <v>0.7573489286396661</v>
+        <v>0.7700774820621815</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.804746424227844</v>
+        <v>8.632104337478278</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09062662492699428</v>
+        <v>0.09036926970293174</v>
       </c>
       <c r="C53">
-        <v>105.5559474896225</v>
+        <v>103.6513604796431</v>
       </c>
       <c r="D53">
-        <v>198.4269474896225</v>
+        <v>198.5433604796431</v>
       </c>
       <c r="E53">
-        <v>82.971</v>
+        <v>84.99199999999999</v>
       </c>
       <c r="F53">
-        <v>103.071</v>
+        <v>105.092</v>
       </c>
       <c r="G53">
         <v>10.2</v>
@@ -5633,28 +5633,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M53">
-        <v>5.5142985</v>
+        <v>5.622422</v>
       </c>
       <c r="N53">
-        <v>42.08570149999996</v>
+        <v>41.97757799999997</v>
       </c>
       <c r="O53">
-        <v>12.62571044999999</v>
+        <v>12.59327339999999</v>
       </c>
       <c r="P53">
-        <v>29.45999104999997</v>
+        <v>29.38430459999998</v>
       </c>
       <c r="Q53">
-        <v>153.85999105</v>
+        <v>153.7843046</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1459737243408047</v>
+        <v>0.1476984785477745</v>
       </c>
       <c r="T53">
-        <v>0.7700774820621815</v>
+        <v>0.7833363918773018</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>8.632104337478278</v>
+        <v>8.466102330988312</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09036926970293174</v>
+        <v>0.09011191447886918</v>
       </c>
       <c r="C54">
-        <v>103.6513604796431</v>
+        <v>101.7469101440393</v>
       </c>
       <c r="D54">
-        <v>198.5433604796431</v>
+        <v>198.6599101440393</v>
       </c>
       <c r="E54">
-        <v>84.99199999999999</v>
+        <v>87.01300000000001</v>
       </c>
       <c r="F54">
-        <v>105.092</v>
+        <v>107.113</v>
       </c>
       <c r="G54">
         <v>10.2</v>
@@ -5715,28 +5715,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M54">
-        <v>5.622422</v>
+        <v>5.7305455</v>
       </c>
       <c r="N54">
-        <v>41.97757799999997</v>
+        <v>41.86945449999997</v>
       </c>
       <c r="O54">
-        <v>12.59327339999999</v>
+        <v>12.56083634999999</v>
       </c>
       <c r="P54">
-        <v>29.38430459999998</v>
+        <v>29.30861814999998</v>
       </c>
       <c r="Q54">
-        <v>153.7843046</v>
+        <v>153.70861815</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1476984785477745</v>
+        <v>0.1494966265507855</v>
       </c>
       <c r="T54">
-        <v>0.7833363918773018</v>
+        <v>0.7971595106207249</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.466102330988312</v>
+        <v>8.306364551158344</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09011191447886918</v>
+        <v>0.08985455925480662</v>
       </c>
       <c r="C55">
-        <v>101.7469101440393</v>
+        <v>99.84259672364594</v>
       </c>
       <c r="D55">
-        <v>198.6599101440393</v>
+        <v>198.776596723646</v>
       </c>
       <c r="E55">
-        <v>87.01300000000001</v>
+        <v>89.03399999999999</v>
       </c>
       <c r="F55">
-        <v>107.113</v>
+        <v>109.134</v>
       </c>
       <c r="G55">
         <v>10.2</v>
@@ -5797,28 +5797,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M55">
-        <v>5.7305455</v>
+        <v>5.838669</v>
       </c>
       <c r="N55">
-        <v>41.86945449999997</v>
+        <v>41.76133099999996</v>
       </c>
       <c r="O55">
-        <v>12.56083634999999</v>
+        <v>12.52839929999999</v>
       </c>
       <c r="P55">
-        <v>29.30861814999998</v>
+        <v>29.23293169999997</v>
       </c>
       <c r="Q55">
-        <v>153.70861815</v>
+        <v>153.6329317</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1494966265507855</v>
+        <v>0.1513729549017535</v>
       </c>
       <c r="T55">
-        <v>0.7971595106207249</v>
+        <v>0.8115836345269056</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.306364551158344</v>
+        <v>8.152542985396151</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08985455925480662</v>
+        <v>0.08959720403074406</v>
       </c>
       <c r="C56">
-        <v>99.84259672364594</v>
+        <v>97.93842045986378</v>
       </c>
       <c r="D56">
-        <v>198.776596723646</v>
+        <v>198.8934204598638</v>
       </c>
       <c r="E56">
-        <v>89.03399999999999</v>
+        <v>91.05500000000001</v>
       </c>
       <c r="F56">
-        <v>109.134</v>
+        <v>111.155</v>
       </c>
       <c r="G56">
         <v>10.2</v>
@@ -5879,28 +5879,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M56">
-        <v>5.838669</v>
+        <v>5.9467925</v>
       </c>
       <c r="N56">
-        <v>41.76133099999996</v>
+        <v>41.65320749999997</v>
       </c>
       <c r="O56">
-        <v>12.52839929999999</v>
+        <v>12.49596224999999</v>
       </c>
       <c r="P56">
-        <v>29.23293169999997</v>
+        <v>29.15724524999997</v>
       </c>
       <c r="Q56">
-        <v>153.6329317</v>
+        <v>153.55724525</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1513729549017535</v>
+        <v>0.1533326756238757</v>
       </c>
       <c r="T56">
-        <v>0.8115836345269056</v>
+        <v>0.8266488306066944</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.152542985396151</v>
+        <v>8.004314931116223</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08959720403074406</v>
+        <v>0.08933984880668153</v>
       </c>
       <c r="C57">
-        <v>97.93842045986378</v>
+        <v>96.03438159466141</v>
       </c>
       <c r="D57">
-        <v>198.8934204598638</v>
+        <v>199.0103815946614</v>
       </c>
       <c r="E57">
-        <v>91.05500000000001</v>
+        <v>93.07599999999999</v>
       </c>
       <c r="F57">
-        <v>111.155</v>
+        <v>113.176</v>
       </c>
       <c r="G57">
         <v>10.2</v>
@@ -5961,28 +5961,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M57">
-        <v>5.9467925</v>
+        <v>6.054916</v>
       </c>
       <c r="N57">
-        <v>41.65320749999997</v>
+        <v>41.54508399999997</v>
       </c>
       <c r="O57">
-        <v>12.49596224999999</v>
+        <v>12.46352519999999</v>
       </c>
       <c r="P57">
-        <v>29.15724524999997</v>
+        <v>29.08155879999997</v>
       </c>
       <c r="Q57">
-        <v>153.55724525</v>
+        <v>153.4815588</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1533326756238757</v>
+        <v>0.1553814745606398</v>
       </c>
       <c r="T57">
-        <v>0.8266488306066944</v>
+        <v>0.8423988083264736</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.004314931116223</v>
+        <v>7.861380735917717</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08933984880668153</v>
+        <v>0.08908249358261897</v>
       </c>
       <c r="C58">
-        <v>96.03438159466141</v>
+        <v>94.1304803705772</v>
       </c>
       <c r="D58">
-        <v>199.0103815946614</v>
+        <v>199.1274803705772</v>
       </c>
       <c r="E58">
-        <v>93.07599999999999</v>
+        <v>95.09700000000001</v>
       </c>
       <c r="F58">
-        <v>113.176</v>
+        <v>115.197</v>
       </c>
       <c r="G58">
         <v>10.2</v>
@@ -6043,28 +6043,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M58">
-        <v>6.054916</v>
+        <v>6.1630395</v>
       </c>
       <c r="N58">
-        <v>41.54508399999997</v>
+        <v>41.43696049999997</v>
       </c>
       <c r="O58">
-        <v>12.46352519999999</v>
+        <v>12.43108814999999</v>
       </c>
       <c r="P58">
-        <v>29.08155879999997</v>
+        <v>29.00587234999998</v>
       </c>
       <c r="Q58">
-        <v>153.4815588</v>
+        <v>153.40587235</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1553814745606398</v>
+        <v>0.1575255664712069</v>
       </c>
       <c r="T58">
-        <v>0.8423988083264736</v>
+        <v>0.8588813431494983</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>7.861380735917717</v>
+        <v>7.72346177563846</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08908249358261897</v>
+        <v>0.08914993835855642</v>
       </c>
       <c r="C59">
-        <v>94.1304803705772</v>
+        <v>92.07877911161881</v>
       </c>
       <c r="D59">
-        <v>199.1274803705772</v>
+        <v>199.0967791116188</v>
       </c>
       <c r="E59">
-        <v>95.09700000000001</v>
+        <v>97.11800000000002</v>
       </c>
       <c r="F59">
-        <v>115.197</v>
+        <v>117.218</v>
       </c>
       <c r="G59">
         <v>10.2</v>
@@ -6125,45 +6125,45 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M59">
-        <v>6.1630395</v>
+        <v>6.364937400000001</v>
       </c>
       <c r="N59">
-        <v>41.43696049999997</v>
+        <v>41.23506259999996</v>
       </c>
       <c r="O59">
-        <v>12.43108814999999</v>
+        <v>12.37051877999999</v>
       </c>
       <c r="P59">
-        <v>29.00587234999998</v>
+        <v>28.86454381999997</v>
       </c>
       <c r="Q59">
-        <v>153.40587235</v>
+        <v>153.26454382</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1575255664712069</v>
+        <v>0.1597717579965629</v>
       </c>
       <c r="T59">
-        <v>0.8588813431494983</v>
+        <v>0.8761487605831432</v>
       </c>
       <c r="U59">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V59">
         <v>0.3</v>
       </c>
       <c r="W59">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y59">
-        <v>7.72346177563846</v>
+        <v>7.478471037279951</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08914993835855642</v>
+        <v>0.08889818313449385</v>
       </c>
       <c r="C60">
-        <v>92.07877911161884</v>
+        <v>90.17242788422568</v>
       </c>
       <c r="D60">
-        <v>199.0967791116188</v>
+        <v>199.2114278842257</v>
       </c>
       <c r="E60">
-        <v>97.11799999999999</v>
+        <v>99.13899999999998</v>
       </c>
       <c r="F60">
-        <v>117.218</v>
+        <v>119.239</v>
       </c>
       <c r="G60">
         <v>10.2</v>
@@ -6207,28 +6207,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M60">
-        <v>6.3649374</v>
+        <v>6.4746777</v>
       </c>
       <c r="N60">
-        <v>41.23506259999996</v>
+        <v>41.12532229999997</v>
       </c>
       <c r="O60">
-        <v>12.37051877999999</v>
+        <v>12.33759668999999</v>
       </c>
       <c r="P60">
-        <v>28.86454381999997</v>
+        <v>28.78772560999997</v>
       </c>
       <c r="Q60">
-        <v>153.26454382</v>
+        <v>153.18772561</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1597717579965629</v>
+        <v>0.1621275198402289</v>
       </c>
       <c r="T60">
-        <v>0.8761487605831431</v>
+        <v>0.8942584910623316</v>
       </c>
       <c r="U60">
         <v>0.0543</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>7.478471037279953</v>
+        <v>7.351717290885377</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08889818313449385</v>
+        <v>0.0886464279104313</v>
       </c>
       <c r="C61">
-        <v>90.17242788422568</v>
+        <v>88.26620877262647</v>
       </c>
       <c r="D61">
-        <v>199.2114278842257</v>
+        <v>199.3262087726265</v>
       </c>
       <c r="E61">
-        <v>99.13899999999998</v>
+        <v>101.16</v>
       </c>
       <c r="F61">
-        <v>119.239</v>
+        <v>121.26</v>
       </c>
       <c r="G61">
         <v>10.2</v>
@@ -6289,28 +6289,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M61">
-        <v>6.4746777</v>
+        <v>6.584417999999999</v>
       </c>
       <c r="N61">
-        <v>41.12532229999997</v>
+        <v>41.01558199999997</v>
       </c>
       <c r="O61">
-        <v>12.33759668999999</v>
+        <v>12.30467459999999</v>
       </c>
       <c r="P61">
-        <v>28.78772560999997</v>
+        <v>28.71090739999998</v>
       </c>
       <c r="Q61">
-        <v>153.18772561</v>
+        <v>153.1109074</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1621275198402289</v>
+        <v>0.1646010697760782</v>
       </c>
       <c r="T61">
-        <v>0.8942584910623316</v>
+        <v>0.9132737080654797</v>
       </c>
       <c r="U61">
         <v>0.0543</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>7.351717290885377</v>
+        <v>7.229188669370622</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0886464279104313</v>
+        <v>0.08839467268636875</v>
       </c>
       <c r="C62">
-        <v>88.26620877262647</v>
+        <v>86.3601220053187</v>
       </c>
       <c r="D62">
-        <v>199.3262087726265</v>
+        <v>199.4411220053187</v>
       </c>
       <c r="E62">
-        <v>101.16</v>
+        <v>103.181</v>
       </c>
       <c r="F62">
-        <v>121.26</v>
+        <v>123.281</v>
       </c>
       <c r="G62">
         <v>10.2</v>
@@ -6371,28 +6371,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M62">
-        <v>6.584417999999999</v>
+        <v>6.6941583</v>
       </c>
       <c r="N62">
-        <v>41.01558199999997</v>
+        <v>40.90584169999997</v>
       </c>
       <c r="O62">
-        <v>12.30467459999999</v>
+        <v>12.27175250999999</v>
       </c>
       <c r="P62">
-        <v>28.71090739999998</v>
+        <v>28.63408918999998</v>
       </c>
       <c r="Q62">
-        <v>153.1109074</v>
+        <v>153.03408919</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1646010697760782</v>
+        <v>0.1672014684265865</v>
       </c>
       <c r="T62">
-        <v>0.9132737080654797</v>
+        <v>0.9332640644021224</v>
       </c>
       <c r="U62">
         <v>0.0543</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.229188669370622</v>
+        <v>7.110677379708808</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08839467268636875</v>
+        <v>0.08814291746230618</v>
       </c>
       <c r="C63">
-        <v>86.3601220053187</v>
+        <v>84.45416781132727</v>
       </c>
       <c r="D63">
-        <v>199.4411220053187</v>
+        <v>199.5561678113273</v>
       </c>
       <c r="E63">
-        <v>103.181</v>
+        <v>105.202</v>
       </c>
       <c r="F63">
-        <v>123.281</v>
+        <v>125.302</v>
       </c>
       <c r="G63">
         <v>10.2</v>
@@ -6453,28 +6453,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M63">
-        <v>6.6941583</v>
+        <v>6.8038986</v>
       </c>
       <c r="N63">
-        <v>40.90584169999997</v>
+        <v>40.79610139999997</v>
       </c>
       <c r="O63">
-        <v>12.27175250999999</v>
+        <v>12.23883041999999</v>
       </c>
       <c r="P63">
-        <v>28.63408918999998</v>
+        <v>28.55727097999998</v>
       </c>
       <c r="Q63">
-        <v>153.03408919</v>
+        <v>152.95727098</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1672014684265865</v>
+        <v>0.1699387301639637</v>
       </c>
       <c r="T63">
-        <v>0.9332640644021224</v>
+        <v>0.9543065447564832</v>
       </c>
       <c r="U63">
         <v>0.0543</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.110677379708808</v>
+        <v>6.995989034874795</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08814291746230618</v>
+        <v>0.08789116223824364</v>
       </c>
       <c r="C64">
-        <v>84.45416781132727</v>
+        <v>82.5483464202057</v>
       </c>
       <c r="D64">
-        <v>199.5561678113273</v>
+        <v>199.6713464202057</v>
       </c>
       <c r="E64">
-        <v>105.202</v>
+        <v>107.223</v>
       </c>
       <c r="F64">
-        <v>125.302</v>
+        <v>127.323</v>
       </c>
       <c r="G64">
         <v>10.2</v>
@@ -6535,28 +6535,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M64">
-        <v>6.8038986</v>
+        <v>6.9136389</v>
       </c>
       <c r="N64">
-        <v>40.79610139999997</v>
+        <v>40.68636109999996</v>
       </c>
       <c r="O64">
-        <v>12.23883041999999</v>
+        <v>12.20590832999999</v>
       </c>
       <c r="P64">
-        <v>28.55727097999998</v>
+        <v>28.48045276999997</v>
       </c>
       <c r="Q64">
-        <v>152.95727098</v>
+        <v>152.88045277</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1699387301639637</v>
+        <v>0.1728239519952531</v>
       </c>
       <c r="T64">
-        <v>0.9543065447564832</v>
+        <v>0.9764864564813501</v>
       </c>
       <c r="U64">
         <v>0.0543</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.995989034874795</v>
+        <v>6.884941589876782</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08789116223824364</v>
+        <v>0.08763940701418109</v>
       </c>
       <c r="C65">
-        <v>82.5483464202057</v>
+        <v>80.64265806203784</v>
       </c>
       <c r="D65">
-        <v>199.6713464202057</v>
+        <v>199.7866580620378</v>
       </c>
       <c r="E65">
-        <v>107.223</v>
+        <v>109.244</v>
       </c>
       <c r="F65">
-        <v>127.323</v>
+        <v>129.344</v>
       </c>
       <c r="G65">
         <v>10.2</v>
@@ -6617,28 +6617,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M65">
-        <v>6.9136389</v>
+        <v>7.0233792</v>
       </c>
       <c r="N65">
-        <v>40.68636109999996</v>
+        <v>40.57662079999997</v>
       </c>
       <c r="O65">
-        <v>12.20590832999999</v>
+        <v>12.17298623999999</v>
       </c>
       <c r="P65">
-        <v>28.48045276999997</v>
+        <v>28.40363455999998</v>
       </c>
       <c r="Q65">
-        <v>152.88045277</v>
+        <v>152.80363456</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1728239519952531</v>
+        <v>0.1758694639282808</v>
       </c>
       <c r="T65">
-        <v>0.9764864564813501</v>
+        <v>0.999898585524265</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.884941589876782</v>
+        <v>6.777364377534957</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08763940701418109</v>
+        <v>0.08738765179011854</v>
       </c>
       <c r="C66">
-        <v>80.64265806203784</v>
+        <v>78.73710296743934</v>
       </c>
       <c r="D66">
-        <v>199.7866580620378</v>
+        <v>199.9021029674394</v>
       </c>
       <c r="E66">
-        <v>109.244</v>
+        <v>111.265</v>
       </c>
       <c r="F66">
-        <v>129.344</v>
+        <v>131.365</v>
       </c>
       <c r="G66">
         <v>10.2</v>
@@ -6699,28 +6699,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M66">
-        <v>7.0233792</v>
+        <v>7.1331195</v>
       </c>
       <c r="N66">
-        <v>40.57662079999997</v>
+        <v>40.46688049999997</v>
       </c>
       <c r="O66">
-        <v>12.17298623999999</v>
+        <v>12.14006414999999</v>
       </c>
       <c r="P66">
-        <v>28.40363455999998</v>
+        <v>28.32681634999998</v>
       </c>
       <c r="Q66">
-        <v>152.80363456</v>
+        <v>152.72681635</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1758694639282808</v>
+        <v>0.1790890051146244</v>
       </c>
       <c r="T66">
-        <v>0.999898585524265</v>
+        <v>1.024648550512489</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>6.777364377534957</v>
+        <v>6.673097233265189</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08738765179011854</v>
+        <v>0.08713589656605598</v>
       </c>
       <c r="C67">
-        <v>78.73710296743934</v>
+        <v>76.83168136755927</v>
       </c>
       <c r="D67">
-        <v>199.9021029674394</v>
+        <v>200.0176813675593</v>
       </c>
       <c r="E67">
-        <v>111.265</v>
+        <v>113.286</v>
       </c>
       <c r="F67">
-        <v>131.365</v>
+        <v>133.386</v>
       </c>
       <c r="G67">
         <v>10.2</v>
@@ -6781,28 +6781,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M67">
-        <v>7.1331195</v>
+        <v>7.2428598</v>
       </c>
       <c r="N67">
-        <v>40.46688049999997</v>
+        <v>40.35714019999997</v>
       </c>
       <c r="O67">
-        <v>12.14006414999999</v>
+        <v>12.10714205999999</v>
       </c>
       <c r="P67">
-        <v>28.32681634999998</v>
+        <v>28.24999813999998</v>
       </c>
       <c r="Q67">
-        <v>152.72681635</v>
+        <v>152.64999814</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1790890051146244</v>
+        <v>0.1824979310766353</v>
       </c>
       <c r="T67">
-        <v>1.024648550512489</v>
+        <v>1.050854395794139</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.673097233265189</v>
+        <v>6.571989699427838</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08713589656605598</v>
+        <v>0.08688414134199343</v>
       </c>
       <c r="C68">
-        <v>76.83168136755927</v>
+        <v>74.9263934940814</v>
       </c>
       <c r="D68">
-        <v>200.0176813675593</v>
+        <v>200.1333934940814</v>
       </c>
       <c r="E68">
-        <v>113.286</v>
+        <v>115.307</v>
       </c>
       <c r="F68">
-        <v>133.386</v>
+        <v>135.407</v>
       </c>
       <c r="G68">
         <v>10.2</v>
@@ -6863,28 +6863,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M68">
-        <v>7.2428598</v>
+        <v>7.352600100000001</v>
       </c>
       <c r="N68">
-        <v>40.35714019999997</v>
+        <v>40.24739989999996</v>
       </c>
       <c r="O68">
-        <v>12.10714205999999</v>
+        <v>12.07421996999999</v>
       </c>
       <c r="P68">
-        <v>28.24999813999998</v>
+        <v>28.17317992999998</v>
       </c>
       <c r="Q68">
-        <v>152.64999814</v>
+        <v>152.57317993</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1824979310766353</v>
+        <v>0.1861134586121013</v>
       </c>
       <c r="T68">
-        <v>1.050854395794139</v>
+        <v>1.078648474123161</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.571989699427838</v>
+        <v>6.473900300928913</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08688414134199343</v>
+        <v>0.08663238611793088</v>
       </c>
       <c r="C69">
-        <v>74.9263934940814</v>
+        <v>73.02123957922612</v>
       </c>
       <c r="D69">
-        <v>200.1333934940814</v>
+        <v>200.2492395792261</v>
       </c>
       <c r="E69">
-        <v>115.307</v>
+        <v>117.328</v>
       </c>
       <c r="F69">
-        <v>135.407</v>
+        <v>137.428</v>
       </c>
       <c r="G69">
         <v>10.2</v>
@@ -6945,28 +6945,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M69">
-        <v>7.352600100000001</v>
+        <v>7.4623404</v>
       </c>
       <c r="N69">
-        <v>40.24739989999996</v>
+        <v>40.13765959999996</v>
       </c>
       <c r="O69">
-        <v>12.07421996999999</v>
+        <v>12.04129787999999</v>
       </c>
       <c r="P69">
-        <v>28.17317992999998</v>
+        <v>28.09636171999998</v>
       </c>
       <c r="Q69">
-        <v>152.57317993</v>
+        <v>152.49636172</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1861134586121013</v>
+        <v>0.189954956618534</v>
       </c>
       <c r="T69">
-        <v>1.078648474123161</v>
+        <v>1.108179682347747</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.473900300928913</v>
+        <v>6.378695884738782</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08663238611793088</v>
+        <v>0.08638063089386833</v>
       </c>
       <c r="C70">
-        <v>73.02123957922612</v>
+        <v>71.11621985575169</v>
       </c>
       <c r="D70">
-        <v>200.2492395792261</v>
+        <v>200.3652198557517</v>
       </c>
       <c r="E70">
-        <v>117.328</v>
+        <v>119.349</v>
       </c>
       <c r="F70">
-        <v>137.428</v>
+        <v>139.449</v>
       </c>
       <c r="G70">
         <v>10.2</v>
@@ -7027,28 +7027,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M70">
-        <v>7.4623404</v>
+        <v>7.572080700000001</v>
       </c>
       <c r="N70">
-        <v>40.13765959999996</v>
+        <v>40.02791929999997</v>
       </c>
       <c r="O70">
-        <v>12.04129787999999</v>
+        <v>12.00837578999999</v>
       </c>
       <c r="P70">
-        <v>28.09636171999998</v>
+        <v>28.01954350999998</v>
       </c>
       <c r="Q70">
-        <v>152.49636172</v>
+        <v>152.41954351</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.189954956618534</v>
+        <v>0.1940442932060269</v>
       </c>
       <c r="T70">
-        <v>1.108179682347747</v>
+        <v>1.139616129812629</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.378695884738782</v>
+        <v>6.286251016844018</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08638063089386833</v>
+        <v>0.08612887566980576</v>
       </c>
       <c r="C71">
-        <v>71.11621985575169</v>
+        <v>69.21133455695602</v>
       </c>
       <c r="D71">
-        <v>200.3652198557517</v>
+        <v>200.481334556956</v>
       </c>
       <c r="E71">
-        <v>119.349</v>
+        <v>121.37</v>
       </c>
       <c r="F71">
-        <v>139.449</v>
+        <v>141.47</v>
       </c>
       <c r="G71">
         <v>10.2</v>
@@ -7109,28 +7109,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M71">
-        <v>7.572080700000001</v>
+        <v>7.681821</v>
       </c>
       <c r="N71">
-        <v>40.02791929999997</v>
+        <v>39.91817899999997</v>
       </c>
       <c r="O71">
-        <v>12.00837578999999</v>
+        <v>11.97545369999999</v>
       </c>
       <c r="P71">
-        <v>28.01954350999998</v>
+        <v>27.94272529999998</v>
       </c>
       <c r="Q71">
-        <v>152.41954351</v>
+        <v>152.3427253</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1940442932060269</v>
+        <v>0.1984062522326859</v>
       </c>
       <c r="T71">
-        <v>1.139616129812629</v>
+        <v>1.173148340441836</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.286251016844018</v>
+        <v>6.196447430889104</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08612887566980576</v>
+        <v>0.08637412044574322</v>
       </c>
       <c r="C72">
-        <v>69.21133455695602</v>
+        <v>67.07722091450557</v>
       </c>
       <c r="D72">
-        <v>200.481334556956</v>
+        <v>200.3682209145056</v>
       </c>
       <c r="E72">
-        <v>121.37</v>
+        <v>123.391</v>
       </c>
       <c r="F72">
-        <v>141.47</v>
+        <v>143.491</v>
       </c>
       <c r="G72">
         <v>10.2</v>
@@ -7191,45 +7191,45 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M72">
-        <v>7.681821</v>
+        <v>7.935052300000001</v>
       </c>
       <c r="N72">
-        <v>39.91817899999997</v>
+        <v>39.66494769999996</v>
       </c>
       <c r="O72">
-        <v>11.97545369999999</v>
+        <v>11.89948430999999</v>
       </c>
       <c r="P72">
-        <v>27.94272529999998</v>
+        <v>27.76546338999997</v>
       </c>
       <c r="Q72">
-        <v>152.3427253</v>
+        <v>152.16546339</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1984062522326859</v>
+        <v>0.2030690360198042</v>
       </c>
       <c r="T72">
-        <v>1.173148340441836</v>
+        <v>1.208993117321334</v>
       </c>
       <c r="U72">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V72">
         <v>0.3</v>
       </c>
       <c r="W72">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y72">
-        <v>6.196447430889104</v>
+        <v>5.9987002228076</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08637412044574322</v>
+        <v>0.08612936522168066</v>
       </c>
       <c r="C73">
-        <v>67.0772209145056</v>
+        <v>65.16910863494047</v>
       </c>
       <c r="D73">
-        <v>200.3682209145056</v>
+        <v>200.4811086349405</v>
       </c>
       <c r="E73">
-        <v>123.391</v>
+        <v>125.412</v>
       </c>
       <c r="F73">
-        <v>143.491</v>
+        <v>145.512</v>
       </c>
       <c r="G73">
         <v>10.2</v>
@@ -7273,28 +7273,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M73">
-        <v>7.9350523</v>
+        <v>8.0468136</v>
       </c>
       <c r="N73">
-        <v>39.66494769999996</v>
+        <v>39.55318639999997</v>
       </c>
       <c r="O73">
-        <v>11.89948430999999</v>
+        <v>11.86595591999999</v>
       </c>
       <c r="P73">
-        <v>27.76546338999997</v>
+        <v>27.68723047999998</v>
       </c>
       <c r="Q73">
-        <v>152.16546339</v>
+        <v>152.08723048</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2030690360198042</v>
+        <v>0.2080648757917166</v>
       </c>
       <c r="T73">
-        <v>1.208993117321333</v>
+        <v>1.247398235406509</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>5.998700222807601</v>
+        <v>5.915384941935273</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08612936522168066</v>
+        <v>0.0858846099976181</v>
       </c>
       <c r="C74">
-        <v>65.16910863494047</v>
+        <v>63.26112362926335</v>
       </c>
       <c r="D74">
-        <v>200.4811086349405</v>
+        <v>200.5941236292634</v>
       </c>
       <c r="E74">
-        <v>125.412</v>
+        <v>127.433</v>
       </c>
       <c r="F74">
-        <v>145.512</v>
+        <v>147.533</v>
       </c>
       <c r="G74">
         <v>10.2</v>
@@ -7355,28 +7355,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M74">
-        <v>8.0468136</v>
+        <v>8.1585749</v>
       </c>
       <c r="N74">
-        <v>39.55318639999997</v>
+        <v>39.44142509999997</v>
       </c>
       <c r="O74">
-        <v>11.86595591999999</v>
+        <v>11.83242752999999</v>
       </c>
       <c r="P74">
-        <v>27.68723047999998</v>
+        <v>27.60899756999998</v>
       </c>
       <c r="Q74">
-        <v>152.08723048</v>
+        <v>152.00899757</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2080648757917166</v>
+        <v>0.2134307777689559</v>
       </c>
       <c r="T74">
-        <v>1.247398235406509</v>
+        <v>1.288648177053549</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>5.915384941935273</v>
+        <v>5.834352271497804</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0858846099976181</v>
+        <v>0.08563985477355555</v>
       </c>
       <c r="C75">
-        <v>63.26112362926335</v>
+        <v>61.35326611283571</v>
       </c>
       <c r="D75">
-        <v>200.5941236292634</v>
+        <v>200.7072661128357</v>
       </c>
       <c r="E75">
-        <v>127.433</v>
+        <v>129.454</v>
       </c>
       <c r="F75">
-        <v>147.533</v>
+        <v>149.554</v>
       </c>
       <c r="G75">
         <v>10.2</v>
@@ -7437,28 +7437,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M75">
-        <v>8.1585749</v>
+        <v>8.270336200000001</v>
       </c>
       <c r="N75">
-        <v>39.44142509999997</v>
+        <v>39.32966379999996</v>
       </c>
       <c r="O75">
-        <v>11.83242752999999</v>
+        <v>11.79889913999999</v>
       </c>
       <c r="P75">
-        <v>27.60899756999998</v>
+        <v>27.53076465999997</v>
       </c>
       <c r="Q75">
-        <v>152.00899757</v>
+        <v>151.93076466</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2134307777689559</v>
+        <v>0.2192094414367521</v>
       </c>
       <c r="T75">
-        <v>1.288648177053549</v>
+        <v>1.333071191134978</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.834352271497804</v>
+        <v>5.755509673234319</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08563985477355555</v>
+        <v>0.08539509954949301</v>
       </c>
       <c r="C76">
-        <v>61.35326611283571</v>
+        <v>59.44553630150529</v>
       </c>
       <c r="D76">
-        <v>200.7072661128357</v>
+        <v>200.8205363015053</v>
       </c>
       <c r="E76">
-        <v>129.454</v>
+        <v>131.475</v>
       </c>
       <c r="F76">
-        <v>149.554</v>
+        <v>151.575</v>
       </c>
       <c r="G76">
         <v>10.2</v>
@@ -7519,28 +7519,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M76">
-        <v>8.270336200000001</v>
+        <v>8.3820975</v>
       </c>
       <c r="N76">
-        <v>39.32966379999996</v>
+        <v>39.21790249999997</v>
       </c>
       <c r="O76">
-        <v>11.79889913999999</v>
+        <v>11.76537074999999</v>
       </c>
       <c r="P76">
-        <v>27.53076465999997</v>
+        <v>27.45253174999998</v>
       </c>
       <c r="Q76">
-        <v>151.93076466</v>
+        <v>151.85253175</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2192094414367521</v>
+        <v>0.225450398197972</v>
       </c>
       <c r="T76">
-        <v>1.333071191134978</v>
+        <v>1.38104804634292</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.755509673234319</v>
+        <v>5.678769544257862</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08539509954949301</v>
+        <v>0.08515034432543045</v>
       </c>
       <c r="C77">
-        <v>59.44553630150529</v>
+        <v>57.53793441160721</v>
       </c>
       <c r="D77">
-        <v>200.8205363015053</v>
+        <v>200.9339344116072</v>
       </c>
       <c r="E77">
-        <v>131.475</v>
+        <v>133.496</v>
       </c>
       <c r="F77">
-        <v>151.575</v>
+        <v>153.596</v>
       </c>
       <c r="G77">
         <v>10.2</v>
@@ -7601,28 +7601,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M77">
-        <v>8.3820975</v>
+        <v>8.4938588</v>
       </c>
       <c r="N77">
-        <v>39.21790249999997</v>
+        <v>39.10614119999997</v>
       </c>
       <c r="O77">
-        <v>11.76537074999999</v>
+        <v>11.73184235999999</v>
       </c>
       <c r="P77">
-        <v>27.45253174999998</v>
+        <v>27.37429883999998</v>
       </c>
       <c r="Q77">
-        <v>151.85253175</v>
+        <v>151.77429884</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.225450398197972</v>
+        <v>0.2322114346892935</v>
       </c>
       <c r="T77">
-        <v>1.38104804634292</v>
+        <v>1.433022972818192</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.678769544257862</v>
+        <v>5.604048892359732</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08515034432543045</v>
+        <v>0.08490558910136789</v>
       </c>
       <c r="C78">
-        <v>57.53793441160721</v>
+        <v>55.63046065996562</v>
       </c>
       <c r="D78">
-        <v>200.9339344116072</v>
+        <v>201.0474606599656</v>
       </c>
       <c r="E78">
-        <v>133.496</v>
+        <v>135.517</v>
       </c>
       <c r="F78">
-        <v>153.596</v>
+        <v>155.617</v>
       </c>
       <c r="G78">
         <v>10.2</v>
@@ -7683,28 +7683,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M78">
-        <v>8.4938588</v>
+        <v>8.605620099999999</v>
       </c>
       <c r="N78">
-        <v>39.10614119999997</v>
+        <v>38.99437989999997</v>
       </c>
       <c r="O78">
-        <v>11.73184235999999</v>
+        <v>11.69831396999999</v>
       </c>
       <c r="P78">
-        <v>27.37429883999998</v>
+        <v>27.29606592999998</v>
       </c>
       <c r="Q78">
-        <v>151.77429884</v>
+        <v>151.69606593</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2322114346892935</v>
+        <v>0.2395603873972517</v>
       </c>
       <c r="T78">
-        <v>1.433022972818192</v>
+        <v>1.4895174581174</v>
       </c>
       <c r="U78">
         <v>0.0553</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.604048892359732</v>
+        <v>5.531269036614802</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08490558910136789</v>
+        <v>0.08466083387730534</v>
       </c>
       <c r="C79">
-        <v>55.63046065996562</v>
+        <v>53.72311526389487</v>
       </c>
       <c r="D79">
-        <v>201.0474606599656</v>
+        <v>201.1611152638949</v>
       </c>
       <c r="E79">
-        <v>135.517</v>
+        <v>137.538</v>
       </c>
       <c r="F79">
-        <v>155.617</v>
+        <v>157.638</v>
       </c>
       <c r="G79">
         <v>10.2</v>
@@ -7765,28 +7765,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M79">
-        <v>8.605620099999999</v>
+        <v>8.717381400000001</v>
       </c>
       <c r="N79">
-        <v>38.99437989999997</v>
+        <v>38.88261859999997</v>
       </c>
       <c r="O79">
-        <v>11.69831396999999</v>
+        <v>11.66478557999999</v>
       </c>
       <c r="P79">
-        <v>27.29606592999998</v>
+        <v>27.21783301999998</v>
       </c>
       <c r="Q79">
-        <v>151.69606593</v>
+        <v>151.61783302</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2395603873972517</v>
+        <v>0.2475774267150243</v>
       </c>
       <c r="T79">
-        <v>1.4895174581174</v>
+        <v>1.551147805716536</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.531269036614802</v>
+        <v>5.460355331017174</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08466083387730534</v>
+        <v>0.08441607865324278</v>
       </c>
       <c r="C80">
-        <v>53.72311526389487</v>
+        <v>51.81589844120111</v>
       </c>
       <c r="D80">
-        <v>201.1611152638949</v>
+        <v>201.2748984412011</v>
       </c>
       <c r="E80">
-        <v>137.538</v>
+        <v>139.559</v>
       </c>
       <c r="F80">
-        <v>157.638</v>
+        <v>159.659</v>
       </c>
       <c r="G80">
         <v>10.2</v>
@@ -7847,28 +7847,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M80">
-        <v>8.717381400000001</v>
+        <v>8.8291427</v>
       </c>
       <c r="N80">
-        <v>38.88261859999997</v>
+        <v>38.77085729999997</v>
       </c>
       <c r="O80">
-        <v>11.66478557999999</v>
+        <v>11.63125718999999</v>
       </c>
       <c r="P80">
-        <v>27.21783301999998</v>
+        <v>27.13960010999998</v>
       </c>
       <c r="Q80">
-        <v>151.61783302</v>
+        <v>151.53960011</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2475774267150243</v>
+        <v>0.2563579935868704</v>
       </c>
       <c r="T80">
-        <v>1.551147805716536</v>
+        <v>1.618647710229875</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.460355331017174</v>
+        <v>5.391236909105565</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08441607865324278</v>
+        <v>0.08417132342918023</v>
       </c>
       <c r="C81">
-        <v>51.81589844120111</v>
+        <v>49.90881041018341</v>
       </c>
       <c r="D81">
-        <v>201.2748984412011</v>
+        <v>201.3888104101834</v>
       </c>
       <c r="E81">
-        <v>139.559</v>
+        <v>141.58</v>
       </c>
       <c r="F81">
-        <v>159.659</v>
+        <v>161.68</v>
       </c>
       <c r="G81">
         <v>10.2</v>
@@ -7929,28 +7929,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M81">
-        <v>8.8291427</v>
+        <v>8.940904000000002</v>
       </c>
       <c r="N81">
-        <v>38.77085729999997</v>
+        <v>38.65909599999996</v>
       </c>
       <c r="O81">
-        <v>11.63125718999999</v>
+        <v>11.59772879999999</v>
       </c>
       <c r="P81">
-        <v>27.13960010999998</v>
+        <v>27.06136719999997</v>
       </c>
       <c r="Q81">
-        <v>151.53960011</v>
+        <v>151.4613672</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2563579935868704</v>
+        <v>0.2660166171459012</v>
       </c>
       <c r="T81">
-        <v>1.618647710229875</v>
+        <v>1.692897605194548</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.391236909105565</v>
+        <v>5.323846447741745</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08417132342918023</v>
+        <v>0.08392656820511768</v>
       </c>
       <c r="C82">
-        <v>49.90881041018341</v>
+        <v>48.00185138963548</v>
       </c>
       <c r="D82">
-        <v>201.3888104101834</v>
+        <v>201.5028513896355</v>
       </c>
       <c r="E82">
-        <v>141.58</v>
+        <v>143.601</v>
       </c>
       <c r="F82">
-        <v>161.68</v>
+        <v>163.701</v>
       </c>
       <c r="G82">
         <v>10.2</v>
@@ -8011,28 +8011,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M82">
-        <v>8.940904000000002</v>
+        <v>9.052665299999999</v>
       </c>
       <c r="N82">
-        <v>38.65909599999996</v>
+        <v>38.54733469999996</v>
       </c>
       <c r="O82">
-        <v>11.59772879999999</v>
+        <v>11.56420040999999</v>
       </c>
       <c r="P82">
-        <v>27.06136719999997</v>
+        <v>26.98313428999997</v>
       </c>
       <c r="Q82">
-        <v>151.4613672</v>
+        <v>151.38313429</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2660166171459012</v>
+        <v>0.276691937921672</v>
       </c>
       <c r="T82">
-        <v>1.692897605194548</v>
+        <v>1.774963278576555</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.323846447741745</v>
+        <v>5.25811994838691</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08392656820511768</v>
+        <v>0.08368181298105512</v>
       </c>
       <c r="C83">
-        <v>48.00185138963548</v>
+        <v>46.0950215988467</v>
       </c>
       <c r="D83">
-        <v>201.5028513896355</v>
+        <v>201.6170215988467</v>
       </c>
       <c r="E83">
-        <v>143.601</v>
+        <v>145.622</v>
       </c>
       <c r="F83">
-        <v>163.701</v>
+        <v>165.722</v>
       </c>
       <c r="G83">
         <v>10.2</v>
@@ -8093,28 +8093,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M83">
-        <v>9.052665299999999</v>
+        <v>9.164426600000001</v>
       </c>
       <c r="N83">
-        <v>38.54733469999996</v>
+        <v>38.43557339999997</v>
       </c>
       <c r="O83">
-        <v>11.56420040999999</v>
+        <v>11.53067201999999</v>
       </c>
       <c r="P83">
-        <v>26.98313428999997</v>
+        <v>26.90490137999998</v>
       </c>
       <c r="Q83">
-        <v>151.38313429</v>
+        <v>151.30490138</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.276691937921672</v>
+        <v>0.2885534054503063</v>
       </c>
       <c r="T83">
-        <v>1.774963278576555</v>
+        <v>1.866147360112119</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.25811994838691</v>
+        <v>5.193996534382191</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08368181298105512</v>
+        <v>0.08343705775699256</v>
       </c>
       <c r="C84">
-        <v>46.0950215988467</v>
+        <v>44.18832125760392</v>
       </c>
       <c r="D84">
-        <v>201.6170215988467</v>
+        <v>201.731321257604</v>
       </c>
       <c r="E84">
-        <v>145.622</v>
+        <v>147.643</v>
       </c>
       <c r="F84">
-        <v>165.722</v>
+        <v>167.743</v>
       </c>
       <c r="G84">
         <v>10.2</v>
@@ -8175,28 +8175,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M84">
-        <v>9.164426600000001</v>
+        <v>9.276187900000002</v>
       </c>
       <c r="N84">
-        <v>38.43557339999997</v>
+        <v>38.32381209999996</v>
       </c>
       <c r="O84">
-        <v>11.53067201999999</v>
+        <v>11.49714362999999</v>
       </c>
       <c r="P84">
-        <v>26.90490137999998</v>
+        <v>26.82666846999997</v>
       </c>
       <c r="Q84">
-        <v>151.30490138</v>
+        <v>151.22666847</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2885534054503063</v>
+        <v>0.3018103397470152</v>
       </c>
       <c r="T84">
-        <v>1.866147360112119</v>
+        <v>1.968058980651866</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.193996534382191</v>
+        <v>5.131418262883609</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08343705775699256</v>
+        <v>0.08319230253293003</v>
       </c>
       <c r="C85">
-        <v>44.18832125760392</v>
+        <v>42.28175058619257</v>
       </c>
       <c r="D85">
-        <v>201.731321257604</v>
+        <v>201.8457505861926</v>
       </c>
       <c r="E85">
-        <v>147.643</v>
+        <v>149.664</v>
       </c>
       <c r="F85">
-        <v>167.743</v>
+        <v>169.764</v>
       </c>
       <c r="G85">
         <v>10.2</v>
@@ -8257,28 +8257,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M85">
-        <v>9.276187900000002</v>
+        <v>9.387949200000001</v>
       </c>
       <c r="N85">
-        <v>38.32381209999996</v>
+        <v>38.21205079999996</v>
       </c>
       <c r="O85">
-        <v>11.49714362999999</v>
+        <v>11.46361523999999</v>
       </c>
       <c r="P85">
-        <v>26.82666846999997</v>
+        <v>26.74843555999998</v>
       </c>
       <c r="Q85">
-        <v>151.22666847</v>
+        <v>151.14843556</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3018103397470152</v>
+        <v>0.3167243908308128</v>
       </c>
       <c r="T85">
-        <v>1.968058980651866</v>
+        <v>2.082709553759083</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.131418262883609</v>
+        <v>5.070329950230233</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08319230253293003</v>
+        <v>0.08294754730886747</v>
       </c>
       <c r="C86">
-        <v>42.2817505861926</v>
+        <v>40.37530980539819</v>
       </c>
       <c r="D86">
-        <v>201.8457505861926</v>
+        <v>201.9603098053982</v>
       </c>
       <c r="E86">
-        <v>149.664</v>
+        <v>151.685</v>
       </c>
       <c r="F86">
-        <v>169.764</v>
+        <v>171.785</v>
       </c>
       <c r="G86">
         <v>10.2</v>
@@ -8339,28 +8339,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M86">
-        <v>9.3879492</v>
+        <v>9.499710500000001</v>
       </c>
       <c r="N86">
-        <v>38.21205079999996</v>
+        <v>38.10028949999997</v>
       </c>
       <c r="O86">
-        <v>11.46361523999999</v>
+        <v>11.43008684999999</v>
       </c>
       <c r="P86">
-        <v>26.74843555999998</v>
+        <v>26.67020264999998</v>
       </c>
       <c r="Q86">
-        <v>151.14843556</v>
+        <v>151.07020265</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3167243908308126</v>
+        <v>0.3336269820591164</v>
       </c>
       <c r="T86">
-        <v>2.082709553759081</v>
+        <v>2.212646869947259</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.070329950230234</v>
+        <v>5.01067900963929</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08294754730886747</v>
+        <v>0.08270279208480491</v>
       </c>
       <c r="C87">
-        <v>40.37530980539819</v>
+        <v>38.46899913650782</v>
       </c>
       <c r="D87">
-        <v>201.9603098053982</v>
+        <v>202.0749991365078</v>
       </c>
       <c r="E87">
-        <v>151.685</v>
+        <v>153.706</v>
       </c>
       <c r="F87">
-        <v>171.785</v>
+        <v>173.806</v>
       </c>
       <c r="G87">
         <v>10.2</v>
@@ -8421,28 +8421,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M87">
-        <v>9.499710500000001</v>
+        <v>9.611471799999999</v>
       </c>
       <c r="N87">
-        <v>38.10028949999997</v>
+        <v>37.98852819999997</v>
       </c>
       <c r="O87">
-        <v>11.43008684999999</v>
+        <v>11.39655845999999</v>
       </c>
       <c r="P87">
-        <v>26.67020264999998</v>
+        <v>26.59196973999998</v>
       </c>
       <c r="Q87">
-        <v>151.07020265</v>
+        <v>150.99196974</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3336269820591164</v>
+        <v>0.3529442291771779</v>
       </c>
       <c r="T87">
-        <v>2.212646869947259</v>
+        <v>2.361146659876606</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.01067900963929</v>
+        <v>4.952415300224881</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08270279208480491</v>
+        <v>0.08245803686074235</v>
       </c>
       <c r="C88">
-        <v>38.46899913650782</v>
+        <v>36.56281880131147</v>
       </c>
       <c r="D88">
-        <v>202.0749991365078</v>
+        <v>202.1898188013115</v>
       </c>
       <c r="E88">
-        <v>153.706</v>
+        <v>155.727</v>
       </c>
       <c r="F88">
-        <v>173.806</v>
+        <v>175.827</v>
       </c>
       <c r="G88">
         <v>10.2</v>
@@ -8503,28 +8503,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M88">
-        <v>9.611471799999999</v>
+        <v>9.7232331</v>
       </c>
       <c r="N88">
-        <v>37.98852819999997</v>
+        <v>37.87676689999996</v>
       </c>
       <c r="O88">
-        <v>11.39655845999999</v>
+        <v>11.36303006999999</v>
       </c>
       <c r="P88">
-        <v>26.59196973999998</v>
+        <v>26.51373682999998</v>
       </c>
       <c r="Q88">
-        <v>150.99196974</v>
+        <v>150.91373683</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3529442291771779</v>
+        <v>0.3752333604672489</v>
       </c>
       <c r="T88">
-        <v>2.361146659876606</v>
+        <v>2.532492571333544</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.952415300224881</v>
+        <v>4.895490986429191</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08245803686074235</v>
+        <v>0.08221328163667982</v>
       </c>
       <c r="C89">
-        <v>36.56281880131147</v>
+        <v>34.65676902210356</v>
       </c>
       <c r="D89">
-        <v>202.1898188013115</v>
+        <v>202.3047690221036</v>
       </c>
       <c r="E89">
-        <v>155.727</v>
+        <v>157.748</v>
       </c>
       <c r="F89">
-        <v>175.827</v>
+        <v>177.848</v>
       </c>
       <c r="G89">
         <v>10.2</v>
@@ -8585,28 +8585,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M89">
-        <v>9.7232331</v>
+        <v>9.834994399999999</v>
       </c>
       <c r="N89">
-        <v>37.87676689999996</v>
+        <v>37.76500559999997</v>
       </c>
       <c r="O89">
-        <v>11.36303006999999</v>
+        <v>11.32950167999999</v>
       </c>
       <c r="P89">
-        <v>26.51373682999998</v>
+        <v>26.43550391999998</v>
       </c>
       <c r="Q89">
-        <v>150.91373683</v>
+        <v>150.83550392</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3752333604672489</v>
+        <v>0.4012373469723318</v>
       </c>
       <c r="T89">
-        <v>2.532492571333544</v>
+        <v>2.732396134699972</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.895490986429191</v>
+        <v>4.839860407037952</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08221328163667982</v>
+        <v>0.08196852641261725</v>
       </c>
       <c r="C90">
-        <v>34.65676902210356</v>
+        <v>32.75085002168424</v>
       </c>
       <c r="D90">
-        <v>202.3047690221036</v>
+        <v>202.4198500216843</v>
       </c>
       <c r="E90">
-        <v>157.748</v>
+        <v>159.769</v>
       </c>
       <c r="F90">
-        <v>177.848</v>
+        <v>179.869</v>
       </c>
       <c r="G90">
         <v>10.2</v>
@@ -8667,28 +8667,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M90">
-        <v>9.834994399999999</v>
+        <v>9.946755700000001</v>
       </c>
       <c r="N90">
-        <v>37.76500559999997</v>
+        <v>37.65324429999997</v>
       </c>
       <c r="O90">
-        <v>11.32950167999999</v>
+        <v>11.29597328999999</v>
       </c>
       <c r="P90">
-        <v>26.43550391999998</v>
+        <v>26.35727100999998</v>
       </c>
       <c r="Q90">
-        <v>150.83550392</v>
+        <v>150.75727101</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4012373469723318</v>
+        <v>0.4319693310237932</v>
       </c>
       <c r="T90">
-        <v>2.732396134699972</v>
+        <v>2.968645800496659</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.839860407037952</v>
+        <v>4.785479953026289</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08196852641261725</v>
+        <v>0.0817237711885547</v>
       </c>
       <c r="C91">
-        <v>32.75085002168424</v>
+        <v>30.84506202336098</v>
       </c>
       <c r="D91">
-        <v>202.4198500216843</v>
+        <v>202.535062023361</v>
       </c>
       <c r="E91">
-        <v>159.769</v>
+        <v>161.79</v>
       </c>
       <c r="F91">
-        <v>179.869</v>
+        <v>181.89</v>
       </c>
       <c r="G91">
         <v>10.2</v>
@@ -8749,28 +8749,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M91">
-        <v>9.946755700000001</v>
+        <v>10.058517</v>
       </c>
       <c r="N91">
-        <v>37.65324429999997</v>
+        <v>37.54148299999996</v>
       </c>
       <c r="O91">
-        <v>11.29597328999999</v>
+        <v>11.26244489999999</v>
       </c>
       <c r="P91">
-        <v>26.35727100999998</v>
+        <v>26.27903809999997</v>
       </c>
       <c r="Q91">
-        <v>150.75727101</v>
+        <v>150.6790381</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4319693310237932</v>
+        <v>0.468847711885547</v>
       </c>
       <c r="T91">
-        <v>2.968645800496659</v>
+        <v>3.252145399452684</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.785479953026289</v>
+        <v>4.732307953548219</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.0817237711885547</v>
+        <v>0.08147901596449214</v>
       </c>
       <c r="C92">
-        <v>30.84506202336098</v>
+        <v>28.93940525094987</v>
       </c>
       <c r="D92">
-        <v>202.535062023361</v>
+        <v>202.6504052509499</v>
       </c>
       <c r="E92">
-        <v>161.79</v>
+        <v>163.811</v>
       </c>
       <c r="F92">
-        <v>181.89</v>
+        <v>183.911</v>
       </c>
       <c r="G92">
         <v>10.2</v>
@@ -8831,28 +8831,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M92">
-        <v>10.058517</v>
+        <v>10.1702783</v>
       </c>
       <c r="N92">
-        <v>37.54148299999996</v>
+        <v>37.42972169999997</v>
       </c>
       <c r="O92">
-        <v>11.26244489999999</v>
+        <v>11.22891650999999</v>
       </c>
       <c r="P92">
-        <v>26.27903809999997</v>
+        <v>26.20080518999998</v>
       </c>
       <c r="Q92">
-        <v>150.6790381</v>
+        <v>150.60080519</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.468847711885547</v>
+        <v>0.5139212884943573</v>
       </c>
       <c r="T92">
-        <v>3.252145399452684</v>
+        <v>3.598644909287826</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.732307953548219</v>
+        <v>4.680304569443293</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08147901596449214</v>
+        <v>0.08123426074042958</v>
       </c>
       <c r="C93">
-        <v>28.93940525094987</v>
+        <v>27.03387992877717</v>
       </c>
       <c r="D93">
-        <v>202.6504052509499</v>
+        <v>202.7658799287772</v>
       </c>
       <c r="E93">
-        <v>163.811</v>
+        <v>165.832</v>
       </c>
       <c r="F93">
-        <v>183.911</v>
+        <v>185.932</v>
       </c>
       <c r="G93">
         <v>10.2</v>
@@ -8913,28 +8913,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M93">
-        <v>10.1702783</v>
+        <v>10.2820396</v>
       </c>
       <c r="N93">
-        <v>37.42972169999997</v>
+        <v>37.31796039999996</v>
       </c>
       <c r="O93">
-        <v>11.22891650999999</v>
+        <v>11.19538811999999</v>
       </c>
       <c r="P93">
-        <v>26.20080518999998</v>
+        <v>26.12257227999997</v>
       </c>
       <c r="Q93">
-        <v>150.60080519</v>
+        <v>150.52257228</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5139212884943573</v>
+        <v>0.57026325925537</v>
       </c>
       <c r="T93">
-        <v>3.598644909287826</v>
+        <v>4.031769296581754</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.680304569443293</v>
+        <v>4.629431693688474</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08123426074042958</v>
+        <v>0.08098950551636702</v>
       </c>
       <c r="C94">
-        <v>27.03387992877717</v>
+        <v>25.12848628168084</v>
       </c>
       <c r="D94">
-        <v>202.7658799287772</v>
+        <v>202.8814862816808</v>
       </c>
       <c r="E94">
-        <v>165.832</v>
+        <v>167.853</v>
       </c>
       <c r="F94">
-        <v>185.932</v>
+        <v>187.953</v>
       </c>
       <c r="G94">
         <v>10.2</v>
@@ -8995,28 +8995,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M94">
-        <v>10.2820396</v>
+        <v>10.3938009</v>
       </c>
       <c r="N94">
-        <v>37.31796039999996</v>
+        <v>37.20619909999996</v>
       </c>
       <c r="O94">
-        <v>11.19538811999999</v>
+        <v>11.16185972999999</v>
       </c>
       <c r="P94">
-        <v>26.12257227999997</v>
+        <v>26.04433936999997</v>
       </c>
       <c r="Q94">
-        <v>150.52257228</v>
+        <v>150.44433937</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.57026325925537</v>
+        <v>0.6427029359481008</v>
       </c>
       <c r="T94">
-        <v>4.031769296581754</v>
+        <v>4.588643508816803</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.629431693688474</v>
+        <v>4.579652858272469</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08098950551636702</v>
+        <v>0.08074475029230448</v>
       </c>
       <c r="C95">
-        <v>25.12848628168084</v>
+        <v>23.2232245350117</v>
       </c>
       <c r="D95">
-        <v>202.8814862816808</v>
+        <v>202.9972245350117</v>
       </c>
       <c r="E95">
-        <v>167.853</v>
+        <v>169.874</v>
       </c>
       <c r="F95">
-        <v>187.953</v>
+        <v>189.974</v>
       </c>
       <c r="G95">
         <v>10.2</v>
@@ -9077,28 +9077,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M95">
-        <v>10.3938009</v>
+        <v>10.5055622</v>
       </c>
       <c r="N95">
-        <v>37.20619909999996</v>
+        <v>37.09443779999997</v>
       </c>
       <c r="O95">
-        <v>11.16185972999999</v>
+        <v>11.12833133999999</v>
       </c>
       <c r="P95">
-        <v>26.04433936999997</v>
+        <v>25.96610645999998</v>
       </c>
       <c r="Q95">
-        <v>150.44433937</v>
+        <v>150.36610646</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6427029359481008</v>
+        <v>0.7392891715384087</v>
       </c>
       <c r="T95">
-        <v>4.588643508816803</v>
+        <v>5.331142458463537</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.579652858272469</v>
+        <v>4.530933147014251</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08074475029230448</v>
+        <v>0.08216249506824193</v>
       </c>
       <c r="C96">
-        <v>23.2232245350117</v>
+        <v>20.53363750319133</v>
       </c>
       <c r="D96">
-        <v>202.9972245350117</v>
+        <v>202.3286375031913</v>
       </c>
       <c r="E96">
-        <v>169.874</v>
+        <v>171.895</v>
       </c>
       <c r="F96">
-        <v>189.974</v>
+        <v>191.995</v>
       </c>
       <c r="G96">
         <v>10.2</v>
@@ -9159,45 +9159,45 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M96">
-        <v>10.5055622</v>
+        <v>11.097311</v>
       </c>
       <c r="N96">
-        <v>37.09443779999997</v>
+        <v>36.50268899999996</v>
       </c>
       <c r="O96">
-        <v>11.12833133999999</v>
+        <v>10.95080669999999</v>
       </c>
       <c r="P96">
-        <v>25.96610645999998</v>
+        <v>25.55188229999997</v>
       </c>
       <c r="Q96">
-        <v>150.36610646</v>
+        <v>149.9518823</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7392891715384087</v>
+        <v>0.8745099013648396</v>
       </c>
       <c r="T96">
-        <v>5.331142458463537</v>
+        <v>6.370640987968964</v>
       </c>
       <c r="U96">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V96">
         <v>0.3</v>
       </c>
       <c r="W96">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y96">
-        <v>4.530933147014251</v>
+        <v>4.289327387508555</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08216249506824193</v>
+        <v>0.08193523984417939</v>
       </c>
       <c r="C97">
-        <v>20.53363750319133</v>
+        <v>18.61951108547171</v>
       </c>
       <c r="D97">
-        <v>202.3286375031913</v>
+        <v>202.4355110854717</v>
       </c>
       <c r="E97">
-        <v>171.895</v>
+        <v>173.916</v>
       </c>
       <c r="F97">
-        <v>191.995</v>
+        <v>194.016</v>
       </c>
       <c r="G97">
         <v>10.2</v>
@@ -9241,28 +9241,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M97">
-        <v>11.097311</v>
+        <v>11.2141248</v>
       </c>
       <c r="N97">
-        <v>36.50268899999996</v>
+        <v>36.38587519999997</v>
       </c>
       <c r="O97">
-        <v>10.95080669999999</v>
+        <v>10.91576255999999</v>
       </c>
       <c r="P97">
-        <v>25.55188229999997</v>
+        <v>25.47011263999998</v>
       </c>
       <c r="Q97">
-        <v>149.9518823</v>
+        <v>149.87011264</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8745099013648396</v>
+        <v>1.077340996104486</v>
       </c>
       <c r="T97">
-        <v>6.370640987968964</v>
+        <v>7.929888782227107</v>
       </c>
       <c r="U97">
         <v>0.0578</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.289327387508555</v>
+        <v>4.244646893888675</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08193523984417939</v>
+        <v>0.08170798462011683</v>
       </c>
       <c r="C98">
-        <v>18.61951108547174</v>
+        <v>16.70549763247337</v>
       </c>
       <c r="D98">
-        <v>202.4355110854717</v>
+        <v>202.5424976324734</v>
       </c>
       <c r="E98">
-        <v>173.916</v>
+        <v>175.937</v>
       </c>
       <c r="F98">
-        <v>194.016</v>
+        <v>196.037</v>
       </c>
       <c r="G98">
         <v>10.2</v>
@@ -9323,28 +9323,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M98">
-        <v>11.2141248</v>
+        <v>11.3309386</v>
       </c>
       <c r="N98">
-        <v>36.38587519999997</v>
+        <v>36.26906139999997</v>
       </c>
       <c r="O98">
-        <v>10.91576255999999</v>
+        <v>10.88071841999999</v>
       </c>
       <c r="P98">
-        <v>25.47011263999998</v>
+        <v>25.38834297999998</v>
       </c>
       <c r="Q98">
-        <v>149.87011264</v>
+        <v>149.78834298</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.077340996104484</v>
+        <v>1.41539282067056</v>
       </c>
       <c r="T98">
-        <v>7.929888782227085</v>
+        <v>10.52863510599065</v>
       </c>
       <c r="U98">
         <v>0.0578</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.244646893888675</v>
+        <v>4.200887647559927</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08170798462011683</v>
+        <v>0.08148072939605427</v>
       </c>
       <c r="C99">
-        <v>16.70549763247337</v>
+        <v>14.79159732339539</v>
       </c>
       <c r="D99">
-        <v>202.5424976324734</v>
+        <v>202.6495973233954</v>
       </c>
       <c r="E99">
-        <v>175.937</v>
+        <v>177.958</v>
       </c>
       <c r="F99">
-        <v>196.037</v>
+        <v>198.058</v>
       </c>
       <c r="G99">
         <v>10.2</v>
@@ -9405,28 +9405,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M99">
-        <v>11.3309386</v>
+        <v>11.4477524</v>
       </c>
       <c r="N99">
-        <v>36.26906139999997</v>
+        <v>36.15224759999997</v>
       </c>
       <c r="O99">
-        <v>10.88071841999999</v>
+        <v>10.84567427999999</v>
       </c>
       <c r="P99">
-        <v>25.38834297999998</v>
+        <v>25.30657331999998</v>
       </c>
       <c r="Q99">
-        <v>149.78834298</v>
+        <v>149.70657332</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.41539282067056</v>
+        <v>2.091496469802712</v>
       </c>
       <c r="T99">
-        <v>10.52863510599065</v>
+        <v>15.72612775351776</v>
       </c>
       <c r="U99">
         <v>0.0578</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.200887647559927</v>
+        <v>4.158021447074621</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08148072939605427</v>
+        <v>0.08125347417199172</v>
       </c>
       <c r="C100">
-        <v>14.79159732339539</v>
+        <v>12.87781033781636</v>
       </c>
       <c r="D100">
-        <v>202.6495973233954</v>
+        <v>202.7568103378163</v>
       </c>
       <c r="E100">
-        <v>177.958</v>
+        <v>179.979</v>
       </c>
       <c r="F100">
-        <v>198.058</v>
+        <v>200.079</v>
       </c>
       <c r="G100">
         <v>10.2</v>
@@ -9487,28 +9487,28 @@
         <v>47.59999999999997</v>
       </c>
       <c r="M100">
-        <v>11.4477524</v>
+        <v>11.5645662</v>
       </c>
       <c r="N100">
-        <v>36.15224759999997</v>
+        <v>36.03543379999996</v>
       </c>
       <c r="O100">
-        <v>10.84567427999999</v>
+        <v>10.81063013999999</v>
       </c>
       <c r="P100">
-        <v>25.30657331999998</v>
+        <v>25.22480365999998</v>
       </c>
       <c r="Q100">
-        <v>149.70657332</v>
+        <v>149.62480366</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.091496469802712</v>
+        <v>4.119807417199168</v>
       </c>
       <c r="T100">
-        <v>15.72612775351776</v>
+        <v>31.31860569609911</v>
       </c>
       <c r="U100">
         <v>0.0578</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.158021447074621</v>
+        <v>4.116021230437504</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08125347417199172</v>
-      </c>
-      <c r="C101">
-        <v>12.87781033781636</v>
-      </c>
-      <c r="D101">
-        <v>202.7568103378163</v>
-      </c>
-      <c r="E101">
-        <v>179.979</v>
-      </c>
-      <c r="F101">
-        <v>200.079</v>
-      </c>
-      <c r="G101">
-        <v>10.2</v>
-      </c>
-      <c r="H101">
-        <v>182</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>172</v>
-      </c>
-      <c r="K101">
-        <v>124.4</v>
-      </c>
-      <c r="L101">
-        <v>47.59999999999997</v>
-      </c>
-      <c r="M101">
-        <v>11.5645662</v>
-      </c>
-      <c r="N101">
-        <v>36.03543379999996</v>
-      </c>
-      <c r="O101">
-        <v>10.81063013999999</v>
-      </c>
-      <c r="P101">
-        <v>25.22480365999998</v>
-      </c>
-      <c r="Q101">
-        <v>149.62480366</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.119807417199168</v>
-      </c>
-      <c r="T101">
-        <v>31.31860569609911</v>
-      </c>
-      <c r="U101">
-        <v>0.0578</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.04046</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Baa2/BBB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.116021230437504</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
